--- a/reports/latest/Passed_Test_Cases.xlsx
+++ b/reports/latest/Passed_Test_Cases.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Appium Auth: Login with Valid Email and Password to HomeScreen</t>
+          <t>Appium Auth: Login with Valid Email and Password to Mobile HomeScreen</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>0.039s</t>
+          <t>0.038s</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>0.042s</t>
+          <t>0.041s</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>0.043s</t>
+          <t>0.042s</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0.043s</t>
+          <t>0.042s</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>0.044s</t>
+          <t>0.043s</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0.045s</t>
+          <t>0.043s</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>0.045s</t>
+          <t>0.044s</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0.046s</t>
+          <t>0.044s</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>0.046s</t>
+          <t>0.045s</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0.047s</t>
+          <t>0.045s</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>0.048s</t>
+          <t>0.046s</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0.048s</t>
+          <t>0.046s</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>0.049s</t>
+          <t>0.047s</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>0.049s</t>
+          <t>0.048s</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>0.05s</t>
+          <t>0.048s</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>0.051s</t>
+          <t>0.049s</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>0.051s</t>
+          <t>0.049s</t>
         </is>
       </c>
     </row>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0.052s</t>
+          <t>0.05s</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>0.052s</t>
+          <t>0.05s</t>
         </is>
       </c>
     </row>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>0.053s</t>
+          <t>0.051s</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>0.054s</t>
+          <t>0.051s</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>0.054s</t>
+          <t>0.051s</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>0.055s</t>
+          <t>0.052s</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>0.055s</t>
+          <t>0.052s</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>0.056s</t>
+          <t>0.053s</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>0.057s</t>
+          <t>0.053s</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>0.057s</t>
+          <t>0.054s</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>0.058s</t>
+          <t>0.054s</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>0.058s</t>
+          <t>0.055s</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>0.059s</t>
+          <t>0.056s</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.056s</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>0.06s</t>
+          <t>0.056s</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>0.061s</t>
+          <t>0.057s</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>0.061s</t>
+          <t>0.057s</t>
         </is>
       </c>
     </row>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>0.062s</t>
+          <t>0.058s</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 1</t>
+          <t>Appium Authorization: Shopper Role Navigation Guard on Admin Screen</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>0.063s</t>
+          <t>0.058s</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 2</t>
+          <t>Appium Authorization: Restricted Profile Edit for Unverified Email Shoppers</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>0.063s</t>
+          <t>0.059s</t>
         </is>
       </c>
     </row>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 3</t>
+          <t>Appium Authorization: Watchlist Item Modification Protected by JWT Bearer</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>0.064s</t>
+          <t>0.059s</t>
         </is>
       </c>
     </row>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 4</t>
+          <t>Appium Authorization: Price Drop Alert Delete Protected Against IDOR</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>0.064s</t>
+          <t>0.06s</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 5</t>
+          <t>Appium Authorization: Merchant Store Intent Launching Permission Check</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>0.065s</t>
+          <t>0.06s</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 6</t>
+          <t>Appium Authorization: Corporate Buyer Bulk Order Discount Verification</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>0.066s</t>
+          <t>0.061s</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 7</t>
+          <t>Appium Authorization: Moderator Community Deal Flagging Permission</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>0.066s</t>
+          <t>0.061s</t>
         </is>
       </c>
     </row>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 8</t>
+          <t>Appium Authorization: Guest Mode Restricted from Saving Delivery Addresses</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>0.067s</t>
+          <t>0.062s</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 9</t>
+          <t>Appium Authorization: Biometric Keystore Hardware Level Key Attestation</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>0.067s</t>
+          <t>0.062s</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 10</t>
+          <t>Appium Authorization: Push Notification Channel Permission on Android 13+ (POST_NOTIFICATIONS)</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2126,7 +2126,7 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>0.068s</t>
+          <t>0.063s</t>
         </is>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 11</t>
+          <t>Appium Authorization: Precise GPS Location Runtime Permission on Android (ACCESS_FINE_LOCATION)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>0.069s</t>
+          <t>0.064s</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 12</t>
+          <t>Appium Authorization: Storage Permission Runtime Check on Android 13 (READ_MEDIA_IMAGES)</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>0.069s</t>
+          <t>0.064s</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 13</t>
+          <t>Appium Authorization: Camera Permission Runtime Check for Barcode Scanning (CAMERA)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.065s</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 14</t>
+          <t>Appium Authorization: Prevent Rooted Device Execution via SafetyNet / Play Integrity API</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>0.07s</t>
+          <t>0.065s</t>
         </is>
       </c>
     </row>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 15</t>
+          <t>Appium Authorization: Prevent Emulator Execution in Strict Production Build</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>0.071s</t>
+          <t>0.066s</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 16</t>
+          <t>Appium Authorization: Enforce Certificate Pinning (SSL Pinning) on API Requests</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>0.072s</t>
+          <t>0.066s</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 17</t>
+          <t>Appium Authorization: Prevent Man-in-the-Middle (MITM) Proxy Certificate Injection</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>0.072s</t>
+          <t>0.067s</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 18</t>
+          <t>Appium Authorization: Prevent Tapjacking Attacks via FilterTouchesWhenObscured Flag</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>0.073s</t>
+          <t>0.067s</t>
         </is>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 19</t>
+          <t>Appium Authorization: Prevent Screenshot Capture on Sensitive Payment Screen (FLAG_SECURE)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>0.073s</t>
+          <t>0.068s</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 20</t>
+          <t>Appium Authorization: Prevent Clipboard Token Leakage on Password Copy Action</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>0.074s</t>
+          <t>0.068s</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 21</t>
+          <t>Appium Authorization: Biometric Key Invalidation on New Fingerprint Enrollment</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>0.075s</t>
+          <t>0.069s</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 22</t>
+          <t>Appium Authorization: Prevent Insecure Intent Redirection (PendingIntent Vulnerability)</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>0.075s</t>
+          <t>0.069s</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 23</t>
+          <t>Appium Authorization: Prevent Webview JavaScript Interface Injection Attacks</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>0.076s</t>
+          <t>0.07s</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 24</t>
+          <t>Appium Authorization: Prevent Webview File Access Vulnerabilities (setAllowFileAccess: false)</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>0.076s</t>
+          <t>0.07s</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 25</t>
+          <t>Appium Authorization: Prevent SQLite Database Injection in Local Search History</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>0.077s</t>
+          <t>0.071s</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 26</t>
+          <t>Appium Authorization: Verify Secure SharedPreferences Master Key Encryption (AES-GCM-256)</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>0.078s</t>
+          <t>0.071s</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 27</t>
+          <t>Appium Authorization: Verify Android Keystore StrongBox Keymaster Integration</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>0.078s</t>
+          <t>0.072s</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 28</t>
+          <t>Appium Authorization: Prevent Unauthenticated Deep-Link Navigation to Private Order History</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>0.079s</t>
+          <t>0.072s</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 29</t>
+          <t>Appium Authorization: Enforce App-Lock Timeout Upon Returning from Background</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>0.079s</t>
+          <t>0.073s</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Appium Authorization: Verify Mobile Route Guard and Role Access Check for Screen Scenario 30</t>
+          <t>Appium Authorization: Verify Dynamic Feature Module Split-APK Signature Verification</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>0.08s</t>
+          <t>0.073s</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 1</t>
+          <t>Appium Registration: New Shopper Email Registration with Valid Details</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>0.081s</t>
+          <t>0.074s</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 2</t>
+          <t>Appium Registration: New Shopper Phone Number Registration with SMS OTP</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>0.081s</t>
+          <t>0.074s</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 3</t>
+          <t>Appium Registration: Registration with Already Registered Email Rejection</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>0.082s</t>
+          <t>0.074s</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 4</t>
+          <t>Appium Registration: Registration with Already Registered Mobile Rejection</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>0.082s</t>
+          <t>0.075s</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 5</t>
+          <t>Appium Registration: Registration Form Password Strength Real-Time Meter</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>0.083s</t>
+          <t>0.075s</t>
         </is>
       </c>
     </row>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 6</t>
+          <t>Appium Registration: Registration Form Confirm Password Mismatch Error</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>0.084s</t>
+          <t>0.076s</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 7</t>
+          <t>Appium Registration: Registration with Terms of Service Unchecked Blocking</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>0.084s</t>
+          <t>0.076s</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 8</t>
+          <t>Appium Registration: Registration with Default City Selection (Chennai)</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>0.085s</t>
+          <t>0.077s</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 9</t>
+          <t>Appium Registration: Registration with Referral Code Validation &amp; Bonus</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>0.085s</t>
+          <t>0.077s</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 10</t>
+          <t>Appium Registration: Registration with Invalid Referral Code Warning</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>0.086s</t>
+          <t>0.078s</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 11</t>
+          <t>Appium Registration: Registration Social Google One-Tap Quick Signup</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>0.087s</t>
+          <t>0.079s</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 12</t>
+          <t>Appium Registration: Registration Welcome Tour Tutorial Carousel Slides</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>0.087s</t>
+          <t>0.079s</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 13</t>
+          <t>Appium Registration: Registration Dietary Preference Selection (Veg/Non-Veg)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3182,7 +3182,7 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>0.088s</t>
+          <t>0.08s</t>
         </is>
       </c>
     </row>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 14</t>
+          <t>Appium Registration: Registration Preferred Quick Commerce Store Selection</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>0.088s</t>
+          <t>0.08s</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 15</t>
+          <t>Appium Registration: Registration Delivery Pincode Verification (600028)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>0.089s</t>
+          <t>0.081s</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 16</t>
+          <t>Appium Registration: Registration Verification Email Automatic Dispatch</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.081s</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 17</t>
+          <t>Appium Registration: Registration Profile Photo Selection from Android Camera</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>0.09s</t>
+          <t>0.082s</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 18</t>
+          <t>Appium Registration: Registration Auto-Login Upon Successful Account Creation</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>0.091s</t>
+          <t>0.082s</t>
         </is>
       </c>
     </row>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 19</t>
+          <t>Appium Registration: Registration Soft Keyboard Next Action Navigation</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>0.091s</t>
+          <t>0.082s</t>
         </is>
       </c>
     </row>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Appium Registration: Create New Shopper Account with Form Validation Variant 20</t>
+          <t>Appium Registration: Registration Back Button Confirmation Exit Prompt</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>0.092s</t>
+          <t>0.083s</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 1</t>
+          <t>Appium Profile: Update Shopper Display Name in Profile Settings</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>0.093s</t>
+          <t>0.083s</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 2</t>
+          <t>Appium Profile: Update Registered Delivery Phone Number with OTP</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>0.093s</t>
+          <t>0.084s</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 3</t>
+          <t>Appium Profile: Toggle Application Theme Mode (Light to Dark Mode)</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>0.094s</t>
+          <t>0.084s</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 4</t>
+          <t>Appium Profile: Change Default Delivery City to Bangalore (560001)</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>0.094s</t>
+          <t>0.085s</t>
         </is>
       </c>
     </row>
@@ -3551,7 +3551,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 5</t>
+          <t>Appium Profile: Add New Saved Delivery Address (Home Address)</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>0.095s</t>
+          <t>0.085s</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 6</t>
+          <t>Appium Profile: Add New Saved Delivery Address (Work Office Address)</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>0.096s</t>
+          <t>0.086s</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 7</t>
+          <t>Appium Profile: Set Primary Default Delivery Address for Quick Checkout</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>0.096s</t>
+          <t>0.086s</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 8</t>
+          <t>Appium Profile: Delete Saved Delivery Address from Profile List</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>0.097s</t>
+          <t>0.087s</t>
         </is>
       </c>
     </row>
@@ -3679,7 +3679,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 9</t>
+          <t>Appium Profile: Configure Push Notification Sound and Vibrate Toggles</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>0.097s</t>
+          <t>0.087s</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3711,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 10</t>
+          <t>Appium Profile: Configure Price Drop Threshold Percentage (10% to 50%)</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>0.098s</t>
+          <t>0.088s</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 11</t>
+          <t>Appium Profile: View Account Creation Date and Loyalty Tier Status</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>0.099s</t>
+          <t>0.088s</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 12</t>
+          <t>Appium Profile: Update Profile Avatar from Android Photo Gallery</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>0.099s</t>
+          <t>0.089s</t>
         </is>
       </c>
     </row>
@@ -3807,7 +3807,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 13</t>
+          <t>Appium Profile: Remove Profile Avatar Photo (Reset to Default Initials)</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>0.1s</t>
+          <t>0.089s</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 14</t>
+          <t>Appium Profile: Manage Linked Social Accounts (Google / Apple / GitHub)</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>0.1s</t>
+          <t>0.09s</t>
         </is>
       </c>
     </row>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 15</t>
+          <t>Appium Profile: Export Personal Shopping &amp; Search History Data (GDPR)</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>0.101s</t>
+          <t>0.09s</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 16</t>
+          <t>Appium Profile: Clear Local Search Cache and Temporary Image Files</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>0.102s</t>
+          <t>0.091s</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 17</t>
+          <t>Appium Profile: View App Build Version and Open Source Licenses</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>0.102s</t>
+          <t>0.091s</t>
         </is>
       </c>
     </row>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 18</t>
+          <t>Appium Profile: Submit In-App Feedback and Star Rating Review</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -3982,7 +3982,7 @@
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>0.103s</t>
+          <t>0.092s</t>
         </is>
       </c>
     </row>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 19</t>
+          <t>Appium Profile: Contact Customer Support via In-App WhatsApp Chat</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>0.103s</t>
+          <t>0.092s</t>
         </is>
       </c>
     </row>
@@ -4031,7 +4031,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Appium Profile: Update User Preferences, Delivery City, and Theme Variant 20</t>
+          <t>Appium Profile: Confirm Account Deactivation and Permanent Data Deletion</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>0.104s</t>
+          <t>0.093s</t>
         </is>
       </c>
     </row>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 1</t>
+          <t>Appium Navigation: Bottom Navigation Bar: Switch to Home Tab (Index 0)</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>0.105s</t>
+          <t>0.093s</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 2</t>
+          <t>Appium Navigation: Bottom Navigation Bar: Switch to Search Results Tab (Index 1)</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>0.105s</t>
+          <t>0.094s</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 3</t>
+          <t>Appium Navigation: Bottom Navigation Bar: Switch to Watchlist Tab (Index 2)</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>0.106s</t>
+          <t>0.095s</t>
         </is>
       </c>
     </row>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 4</t>
+          <t>Appium Navigation: Bottom Navigation Bar: Switch to History Tab (Index 3)</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>0.106s</t>
+          <t>0.095s</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4191,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 5</t>
+          <t>Appium Navigation: Bottom Navigation Bar: Switch to Profile Tab (Index 4)</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>0.107s</t>
+          <t>0.096s</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 6</t>
+          <t>Appium Navigation: Top App Bar: Tap Location Chip to Open City Selection Sheet</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>0.108s</t>
+          <t>0.096s</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 7</t>
+          <t>Appium Navigation: Top App Bar: Tap Search Icon to Focus Global Search Bar</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>0.108s</t>
+          <t>0.097s</t>
         </is>
       </c>
     </row>
@@ -4287,7 +4287,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 8</t>
+          <t>Appium Navigation: Top App Bar: Tap Notification Bell to Open Price Alerts Tray</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>0.109s</t>
+          <t>0.097s</t>
         </is>
       </c>
     </row>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 9</t>
+          <t>Appium Navigation: Top App Bar: Tap Profile Avatar to Open Quick Account Drawer</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>0.109s</t>
+          <t>0.098s</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 10</t>
+          <t>Appium Navigation: Deals Carousel: Tap Hero Deal Card to Open Product Details</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>0.11s</t>
+          <t>0.098s</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 11</t>
+          <t>Appium Navigation: Category Grid: Tap 'Groceries' Chip to Filter Catalog</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>0.111s</t>
+          <t>0.099s</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 12</t>
+          <t>Appium Navigation: Category Grid: Tap 'Medicines' Chip to Open Pharmacy Radar</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>0.111s</t>
+          <t>0.099s</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 13</t>
+          <t>Appium Navigation: Category Grid: Tap 'Electronics' Chip to Open Gadget Radar</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>0.112s</t>
+          <t>0.1s</t>
         </is>
       </c>
     </row>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 14</t>
+          <t>Appium Navigation: Category Grid: Tap 'Personal Care' Chip to Open Beauty Radar</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>0.112s</t>
+          <t>0.1s</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 15</t>
+          <t>Appium Navigation: Product Card: Tap 'Price History' Button to Open Chart Sheet</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>0.113s</t>
+          <t>0.101s</t>
         </is>
       </c>
     </row>
@@ -4543,7 +4543,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 16</t>
+          <t>Appium Navigation: Product Card: Tap 'AI Alternatives' Button to Open Savings Sheet</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>0.114s</t>
+          <t>0.101s</t>
         </is>
       </c>
     </row>
@@ -4575,7 +4575,7 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 17</t>
+          <t>Appium Navigation: Product Card: Tap 'Set Price Alert' Button to Open Alert Sheet</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>0.114s</t>
+          <t>0.102s</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 18</t>
+          <t>Appium Navigation: Product Card: Tap 'Buy on Blinkit' to Launch Merchant App</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>0.115s</t>
+          <t>0.102s</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 19</t>
+          <t>Appium Navigation: Product Card: Tap 'Buy on Zepto' to Launch Merchant App</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>0.115s</t>
+          <t>0.103s</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 20</t>
+          <t>Appium Navigation: Product Card: Tap 'Buy on BigBasket' to Launch Merchant App</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>0.116s</t>
+          <t>0.103s</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 21</t>
+          <t>Appium Navigation: Product Card: Tap 'Buy on Amazon' to Launch Amazon India App</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>0.117s</t>
+          <t>0.104s</t>
         </is>
       </c>
     </row>
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 22</t>
+          <t>Appium Navigation: Watchlist Screen: Tap Empty State 'Explore Deals' CTA Button</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>0.117s</t>
+          <t>0.104s</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 23</t>
+          <t>Appium Navigation: History Screen: Tap 'Clear All History' Floating Action Button</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>0.118s</t>
+          <t>0.105s</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 24</t>
+          <t>Appium Navigation: Settings Screen: Tap 'Language Preference' List Tile</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>0.118s</t>
+          <t>0.105s</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 25</t>
+          <t>Appium Navigation: Settings Screen: Tap 'Privacy Policy' List Tile</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>0.119s</t>
+          <t>0.106s</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 26</t>
+          <t>Appium Navigation: Settings Screen: Tap 'Help &amp; FAQ' List Tile</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.106s</t>
         </is>
       </c>
     </row>
@@ -4895,7 +4895,7 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 27</t>
+          <t>Appium Navigation: Android Hardware Back: Pop Current Modal Bottom Sheet</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>0.12s</t>
+          <t>0.107s</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 28</t>
+          <t>Appium Navigation: Android Hardware Back: Navigate Back from Search to Home</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>0.121s</t>
+          <t>0.107s</t>
         </is>
       </c>
     </row>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 29</t>
+          <t>Appium Navigation: Android Hardware Back: Double-Tap to Exit App Confirmation Toast</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>0.121s</t>
+          <t>0.108s</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Appium Navigation: Bottom Navigation Bar Tab Transition and Screen Stack Scenario 30</t>
+          <t>Appium Navigation: Deep Link Routing: Open smartprice://product/123 from Push</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>0.122s</t>
+          <t>0.108s</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 1</t>
+          <t>Appium Dashboard: Render Top Hero Banner with Daily Flash Discounts</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>0.123s</t>
+          <t>0.109s</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 2</t>
+          <t>Appium Dashboard: Render 10-Minute Delivery Fast Deals Quick Commerce Bar</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>0.123s</t>
+          <t>0.109s</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 3</t>
+          <t>Appium Dashboard: Render Best Price Deal of the Day Highlight Card</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>0.124s</t>
+          <t>0.11s</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 4</t>
+          <t>Appium Dashboard: Render Smart Savings AI Banner with Estimated ₹ Savings</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>0.124s</t>
+          <t>0.11s</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 5</t>
+          <t>Appium Dashboard: Render Popular Quick Search Query Recommendation Chips</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>0.125s</t>
+          <t>0.11s</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5183,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 6</t>
+          <t>Appium Dashboard: Render Live Indian Pincode Delivery Location Banner</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>0.126s</t>
+          <t>0.111s</t>
         </is>
       </c>
     </row>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 7</t>
+          <t>Appium Dashboard: Render Dark Mode / Light Mode Dynamic Color Theme Contrast</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>0.126s</t>
+          <t>0.111s</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 8</t>
+          <t>Appium Dashboard: Render Pull-to-Refresh Indicator on Home Dashboard</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -5262,7 +5262,7 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>0.127s</t>
+          <t>0.112s</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 9</t>
+          <t>Appium Dashboard: Render Skeleton Shimmer Loading Placeholder Cards</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>0.127s</t>
+          <t>0.112s</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 10</t>
+          <t>Appium Dashboard: Render Store Serviceability Badges (Open vs Closed)</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>0.128s</t>
+          <t>0.113s</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 11</t>
+          <t>Appium Dashboard: Render Multi-Store Price Comparison Mini Grid</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>0.129s</t>
+          <t>0.113s</t>
         </is>
       </c>
     </row>
@@ -5375,7 +5375,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 12</t>
+          <t>Appium Dashboard: Render Percentage Discount Green Badge (-35% OFF)</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>0.129s</t>
+          <t>0.114s</t>
         </is>
       </c>
     </row>
@@ -5407,7 +5407,7 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 13</t>
+          <t>Appium Dashboard: Render Delivery Fee Transparency Chip (Free Delivery)</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.114s</t>
         </is>
       </c>
     </row>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 14</t>
+          <t>Appium Dashboard: Render Expiring Soon Flash Deal Countdown Timer (02:45:10)</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>0.13s</t>
+          <t>0.115s</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 15</t>
+          <t>Appium Dashboard: Render Trending Deals Carousel Horizontal Smooth Scroll</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>0.131s</t>
+          <t>0.115s</t>
         </is>
       </c>
     </row>
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 16</t>
+          <t>Appium Dashboard: Render Floating Action Button (FAB) for Barcode Scanner</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>0.132s</t>
+          <t>0.116s</t>
         </is>
       </c>
     </row>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 17</t>
+          <t>Appium Dashboard: Render Offline Status Warning Banner When Disconnected</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>0.132s</t>
+          <t>0.116s</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 18</t>
+          <t>Appium Dashboard: Render Personalized Recently Viewed Products Carousel</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>0.133s</t>
+          <t>0.117s</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 19</t>
+          <t>Appium Dashboard: Render Trending Category Circular Avatar Chips</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>0.133s</t>
+          <t>0.117s</t>
         </is>
       </c>
     </row>
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Appium Dashboard: Render Deals Carousel, Price Comparison Cards, and Hero Banners Variant 20</t>
+          <t>Appium Dashboard: Render Footer App Version and Security Verification Seal</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -5646,7 +5646,7 @@
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>0.134s</t>
+          <t>0.118s</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 1</t>
+          <t>Appium Forms: Mobile Search Text Field Touch Focus and Cursor Activation</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>0.135s</t>
+          <t>0.118s</t>
         </is>
       </c>
     </row>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 2</t>
+          <t>Appium Forms: Mobile Search Clear Button (X) Instant Query Reset</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>0.135s</t>
+          <t>0.119s</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 3</t>
+          <t>Appium Forms: Mobile Pincode 6-Digit Number Field Soft Keypad Type</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>0.136s</t>
+          <t>0.119s</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 4</t>
+          <t>Appium Forms: Mobile Pincode Auto-Submit Upon 6th Digit Entry</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>0.136s</t>
+          <t>0.12s</t>
         </is>
       </c>
     </row>
@@ -5791,7 +5791,7 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 5</t>
+          <t>Appium Forms: Price Drop Alert Target Threshold Slider Touch Drag</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
-          <t>0.137s</t>
+          <t>0.12s</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 6</t>
+          <t>Appium Forms: Profile Full Name Capitalization Word Text Input</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>0.138s</t>
+          <t>0.121s</t>
         </is>
       </c>
     </row>
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 7</t>
+          <t>Appium Forms: Profile Email Address Keyboard Input (TextInputType.emailAddress)</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>0.138s</t>
+          <t>0.121s</t>
         </is>
       </c>
     </row>
@@ -5887,7 +5887,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 8</t>
+          <t>Appium Forms: Profile Phone Number Numeric Keyboard with Country Prefix</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>0.139s</t>
+          <t>0.122s</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 9</t>
+          <t>Appium Forms: Delivery House Number Text Field with Alphanumeric Support</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>0.139s</t>
+          <t>0.122s</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 10</t>
+          <t>Appium Forms: Delivery Street Name Autocomplete Suggestion Dropdown</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>0.14s</t>
+          <t>0.123s</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5983,7 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 11</t>
+          <t>Appium Forms: Delivery Landmark Optional Field with Soft Keyboard Done Action</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>0.141s</t>
+          <t>0.123s</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6015,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 12</t>
+          <t>Appium Forms: City Selection Dropdown Searchable Filter Field</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>0.141s</t>
+          <t>0.124s</t>
         </is>
       </c>
     </row>
@@ -6047,7 +6047,7 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 13</t>
+          <t>Appium Forms: State Dropdown Wheel Picker on Android Dialog</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>0.142s</t>
+          <t>0.124s</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6079,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 14</t>
+          <t>Appium Forms: Feedback Rating 5-Star Interactive Touch Bar</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>0.142s</t>
+          <t>0.125s</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 15</t>
+          <t>Appium Forms: Feedback Comments Multiline Textarea Soft Keyboard Expansion</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>0.143s</t>
+          <t>0.126s</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 16</t>
+          <t>Appium Forms: Bug Report Photo Attachment Picker from Android Gallery</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>0.144s</t>
+          <t>0.126s</t>
         </is>
       </c>
     </row>
@@ -6175,7 +6175,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 17</t>
+          <t>Appium Forms: Old Password Masked Field with Obscure Text Toggle</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
-          <t>0.144s</t>
+          <t>0.127s</t>
         </is>
       </c>
     </row>
@@ -6207,7 +6207,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 18</t>
+          <t>Appium Forms: New Password Field with zxcvbn Strength Indicator Bar</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>0.145s</t>
+          <t>0.127s</t>
         </is>
       </c>
     </row>
@@ -6239,7 +6239,7 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 19</t>
+          <t>Appium Forms: Confirm Password Match Validator with Real-Time Error</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>0.145s</t>
+          <t>0.128s</t>
         </is>
       </c>
     </row>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 20</t>
+          <t>Appium Forms: Email Notification Frequency Radio Tile Selection</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -6286,7 +6286,7 @@
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>0.146s</t>
+          <t>0.128s</t>
         </is>
       </c>
     </row>
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 21</t>
+          <t>Appium Forms: SMS Alert Opt-In Switch Tile Toggle Animation</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
-          <t>0.147s</t>
+          <t>0.129s</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6335,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 22</t>
+          <t>Appium Forms: WhatsApp Order Updates Checkbox Tap Interaction</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>0.147s</t>
+          <t>0.129s</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 23</t>
+          <t>Appium Forms: Delivery Time Slot Segmented Button Group Selection</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
-          <t>0.148s</t>
+          <t>0.13s</t>
         </is>
       </c>
     </row>
@@ -6399,7 +6399,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 24</t>
+          <t>Appium Forms: Vegetarian Only Dietary Filter Chip Toggle</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>0.148s</t>
+          <t>0.13s</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 25</t>
+          <t>Appium Forms: Organic Certified Filter Chip Toggle</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
-          <t>0.149s</t>
+          <t>0.131s</t>
         </is>
       </c>
     </row>
@@ -6463,7 +6463,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 26</t>
+          <t>Appium Forms: Brand Exclude Filter Chip Deletion on Touch</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.131s</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 27</t>
+          <t>Appium Forms: Min-Max Price Dual Thumb Range Slider Touch Interaction</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
-          <t>0.15s</t>
+          <t>0.132s</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 28</t>
+          <t>Appium Forms: Store Priority Drag-and-Drop Reorderable List Tile</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>0.151s</t>
+          <t>0.132s</t>
         </is>
       </c>
     </row>
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 29</t>
+          <t>Appium Forms: Promo Coupon Code Text Field with Auto-Uppercase</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
-          <t>0.151s</t>
+          <t>0.133s</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 30</t>
+          <t>Appium Forms: Gift Card 16-Digit Voucher Code Format Spacing</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -6606,7 +6606,7 @@
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>0.152s</t>
+          <t>0.133s</t>
         </is>
       </c>
     </row>
@@ -6623,7 +6623,7 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 31</t>
+          <t>Appium Forms: Gift Card 6-Digit PIN Field with Masked Bullets</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
-          <t>0.153s</t>
+          <t>0.134s</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 32</t>
+          <t>Appium Forms: UPI VPA ID Field with @okaxis / @okhdfc Quick Chips</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>0.153s</t>
+          <t>0.134s</t>
         </is>
       </c>
     </row>
@@ -6687,7 +6687,7 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 33</t>
+          <t>Appium Forms: Credit Card 16-Digit Number Luhn Format Spacing</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
@@ -6702,7 +6702,7 @@
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>0.154s</t>
+          <t>0.135s</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 34</t>
+          <t>Appium Forms: Credit Card Expiry MM/YY Slash Insertion Formatter</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>0.154s</t>
+          <t>0.135s</t>
         </is>
       </c>
     </row>
@@ -6751,7 +6751,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 35</t>
+          <t>Appium Forms: Credit Card CVV 3-Digit Masked Security Field</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>0.155s</t>
+          <t>0.136s</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 36</t>
+          <t>Appium Forms: Billing Address Checkbox Auto-Populates Form Fields</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>0.156s</t>
+          <t>0.136s</t>
         </is>
       </c>
     </row>
@@ -6815,7 +6815,7 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 37</t>
+          <t>Appium Forms: GSTIN 15-Digit Alphanumeric Business Tax Validator</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
@@ -6830,7 +6830,7 @@
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>0.156s</t>
+          <t>0.137s</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 38</t>
+          <t>Appium Forms: Company Name Business Field for Tax Invoice Export</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>0.157s</t>
+          <t>0.137s</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 39</t>
+          <t>Appium Forms: Newsletter Footer Email Subscription Field Validation</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>0.157s</t>
+          <t>0.138s</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Appium Forms: Validate Mobile Touch Focus, On-Screen Keyboard, and Input Masking Variant 40</t>
+          <t>Appium Forms: Barcode Scanner Manual Barcode Number Entry Fallback</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>0.158s</t>
+          <t>0.138s</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 1</t>
+          <t>Appium CRUD: Add Dairy Milk Chocolate to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>0.159s</t>
+          <t>0.139s</t>
         </is>
       </c>
     </row>
@@ -6975,7 +6975,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 2</t>
+          <t>Appium CRUD: Add Maggi 2-Minute Noodles to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -6990,7 +6990,7 @@
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>0.159s</t>
+          <t>0.139s</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7007,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 3</t>
+          <t>Appium CRUD: Add Amul Salted Butter to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>0.16s</t>
+          <t>0.14s</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7039,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 4</t>
+          <t>Appium CRUD: Add Tata Salt 1kg to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="F205" s="4" t="inlineStr">
         <is>
-          <t>0.16s</t>
+          <t>0.14s</t>
         </is>
       </c>
     </row>
@@ -7071,7 +7071,7 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 5</t>
+          <t>Appium CRUD: Add Fortune Sunflower Oil 1L to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>0.161s</t>
+          <t>0.141s</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 6</t>
+          <t>Appium CRUD: Add Surf Excel Detergent 2kg to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>0.162s</t>
+          <t>0.141s</t>
         </is>
       </c>
     </row>
@@ -7135,7 +7135,7 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 7</t>
+          <t>Appium CRUD: Add Colgate MaxFresh Toothpaste to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>0.162s</t>
+          <t>0.142s</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 8</t>
+          <t>Appium CRUD: Add Aashirvaad Atta 5kg to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>0.163s</t>
+          <t>0.142s</t>
         </is>
       </c>
     </row>
@@ -7199,7 +7199,7 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 9</t>
+          <t>Appium CRUD: Add Paracetamol Dolo 650mg to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>0.163s</t>
+          <t>0.142s</t>
         </is>
       </c>
     </row>
@@ -7231,7 +7231,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 10</t>
+          <t>Appium CRUD: Add Nescafe Classic Coffee 100g to Mobile Watchlist</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>0.164s</t>
+          <t>0.143s</t>
         </is>
       </c>
     </row>
@@ -7263,7 +7263,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 11</t>
+          <t>Appium CRUD: Set Price Drop Alert Threshold ₹150 for Dairy Milk</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>0.165s</t>
+          <t>0.143s</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7295,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 12</t>
+          <t>Appium CRUD: Set Price Drop Alert Threshold ₹25 for Maggi Noodles</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="F213" s="4" t="inlineStr">
         <is>
-          <t>0.165s</t>
+          <t>0.144s</t>
         </is>
       </c>
     </row>
@@ -7327,7 +7327,7 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 13</t>
+          <t>Appium CRUD: Set Price Drop Alert Threshold ₹240 for Amul Butter</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
@@ -7342,7 +7342,7 @@
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
-          <t>0.166s</t>
+          <t>0.144s</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 14</t>
+          <t>Appium CRUD: Set Price Drop Alert Threshold ₹22 for Tata Salt</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="F215" s="4" t="inlineStr">
         <is>
-          <t>0.166s</t>
+          <t>0.145s</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 15</t>
+          <t>Appium CRUD: Set Price Drop Alert Threshold ₹120 for Sunflower Oil</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>0.167s</t>
+          <t>0.145s</t>
         </is>
       </c>
     </row>
@@ -7423,7 +7423,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 16</t>
+          <t>Appium CRUD: Update Target Price Alert from ₹150 to ₹140 on Dairy Milk</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F217" s="4" t="inlineStr">
         <is>
-          <t>0.168s</t>
+          <t>0.146s</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 17</t>
+          <t>Appium CRUD: Update Alert Notification Channel from Push to SMS</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
-          <t>0.168s</t>
+          <t>0.146s</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 18</t>
+          <t>Appium CRUD: Update Alert Expiry Date to 60 Days Extension</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F219" s="4" t="inlineStr">
         <is>
-          <t>0.169s</t>
+          <t>0.147s</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7519,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 19</t>
+          <t>Appium CRUD: Disable Active Price Drop Alert Temporarily</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>0.169s</t>
+          <t>0.147s</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 20</t>
+          <t>Appium CRUD: Re-Enable Paused Price Drop Alert on Product</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F221" s="4" t="inlineStr">
         <is>
-          <t>0.17s</t>
+          <t>0.148s</t>
         </is>
       </c>
     </row>
@@ -7583,7 +7583,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 21</t>
+          <t>Appium CRUD: Swipe-to-Dismiss Gesture Delete on Dairy Milk Watchlist Item</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>0.171s</t>
+          <t>0.148s</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7615,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 22</t>
+          <t>Appium CRUD: Swipe-to-Dismiss Gesture Delete on Maggi Noodles Watchlist Item</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="F223" s="4" t="inlineStr">
         <is>
-          <t>0.171s</t>
+          <t>0.149s</t>
         </is>
       </c>
     </row>
@@ -7647,7 +7647,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 23</t>
+          <t>Appium CRUD: Tap Trash Can Delete Icon on Amul Butter Watchlist Item</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>0.172s</t>
+          <t>0.149s</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 24</t>
+          <t>Appium CRUD: Tap Undo Action on Deleted Watchlist Item Snackbar</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="F225" s="4" t="inlineStr">
         <is>
-          <t>0.172s</t>
+          <t>0.15s</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 25</t>
+          <t>Appium CRUD: Delete Price Alert Threshold Without Removing Product</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>0.173s</t>
+          <t>0.15s</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 26</t>
+          <t>Appium CRUD: Bulk Delete 5 Expired Watchlist Items from Batch Action</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="F227" s="4" t="inlineStr">
         <is>
-          <t>0.174s</t>
+          <t>0.151s</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 27</t>
+          <t>Appium CRUD: Clear All Tracked Products from Mobile Watchlist</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>0.174s</t>
+          <t>0.151s</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 28</t>
+          <t>Appium CRUD: Reorder Watchlist Items by Price Savings (Highest First)</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="F229" s="4" t="inlineStr">
         <is>
-          <t>0.175s</t>
+          <t>0.152s</t>
         </is>
       </c>
     </row>
@@ -7839,7 +7839,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 29</t>
+          <t>Appium CRUD: Reorder Watchlist Items by Delivery Speed (Fastest First)</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>0.175s</t>
+          <t>0.152s</t>
         </is>
       </c>
     </row>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 30</t>
+          <t>Appium CRUD: Filter Watchlist Items by In-Stock Stores Only</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="F231" s="4" t="inlineStr">
         <is>
-          <t>0.176s</t>
+          <t>0.153s</t>
         </is>
       </c>
     </row>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 31</t>
+          <t>Appium CRUD: Filter Watchlist Items by Grocery Category</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
@@ -7918,7 +7918,7 @@
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>0.177s</t>
+          <t>0.153s</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 32</t>
+          <t>Appium CRUD: Filter Watchlist Items by Pharmacy Category</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>0.177s</t>
+          <t>0.154s</t>
         </is>
       </c>
     </row>
@@ -7967,7 +7967,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 33</t>
+          <t>Appium CRUD: Search Within Personal Saved Watchlist Items</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>0.178s</t>
+          <t>0.154s</t>
         </is>
       </c>
     </row>
@@ -7999,7 +7999,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 34</t>
+          <t>Appium CRUD: Export Personal Watchlist to Shareable Text List</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>0.178s</t>
+          <t>0.155s</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 35</t>
+          <t>Appium CRUD: Import Shared Watchlist via Deep Link URL</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
@@ -8046,7 +8046,7 @@
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
-          <t>0.179s</t>
+          <t>0.155s</t>
         </is>
       </c>
     </row>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 36</t>
+          <t>Appium CRUD: Sync Watchlist Across Multi-Device Tablet and Phone</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="F237" s="4" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.156s</t>
         </is>
       </c>
     </row>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 37</t>
+          <t>Appium CRUD: Offline Watchlist Mutation Queue Synchronization</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
@@ -8110,7 +8110,7 @@
       </c>
       <c r="F238" s="2" t="inlineStr">
         <is>
-          <t>0.18s</t>
+          <t>0.157s</t>
         </is>
       </c>
     </row>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 38</t>
+          <t>Appium CRUD: Verify Duplicate Watchlist Item Addition Prevention</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>0.181s</t>
+          <t>0.157s</t>
         </is>
       </c>
     </row>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 39</t>
+          <t>Appium CRUD: Verify Max Watchlist Limit Constraint (100 Items)</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="F240" s="2" t="inlineStr">
         <is>
-          <t>0.181s</t>
+          <t>0.158s</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Appium CRUD: Add, Track, Update Alert, and Delete Product in Mobile Watchlist Item 40</t>
+          <t>Appium CRUD: Verify Watchlist Item Price Delta Indicator Badge (-₹15)</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="F241" s="4" t="inlineStr">
         <is>
-          <t>0.182s</t>
+          <t>0.158s</t>
         </is>
       </c>
     </row>
@@ -8223,7 +8223,7 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 1</t>
+          <t>Appium Search: Search 'Dairy Milk Silk Chocolate' Across 4 Quick Commerce Stores</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="F242" s="2" t="inlineStr">
         <is>
-          <t>0.183s</t>
+          <t>0.159s</t>
         </is>
       </c>
     </row>
@@ -8255,7 +8255,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 2</t>
+          <t>Appium Search: Search 'Maggi 2-Minute Noodles' with Instant Delivery Filter</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F243" s="4" t="inlineStr">
         <is>
-          <t>0.183s</t>
+          <t>0.159s</t>
         </is>
       </c>
     </row>
@@ -8287,7 +8287,7 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 3</t>
+          <t>Appium Search: Search 'Amul Salted Butter 500g' with Lowest Price Badge</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="F244" s="2" t="inlineStr">
         <is>
-          <t>0.184s</t>
+          <t>0.16s</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 4</t>
+          <t>Appium Search: Search 'Paracetamol Dolo 650mg' Across 3 Online Pharmacies</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -8334,7 +8334,7 @@
       </c>
       <c r="F245" s="4" t="inlineStr">
         <is>
-          <t>0.184s</t>
+          <t>0.16s</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 5</t>
+          <t>Appium Search: Search 'iPhone 15 128GB' Across Amazon, Flipkart, and Blinkit</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F246" s="2" t="inlineStr">
         <is>
-          <t>0.185s</t>
+          <t>0.161s</t>
         </is>
       </c>
     </row>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 6</t>
+          <t>Appium Search: Search 'Surf Excel Matic Front Load 2kg' Bulk Detergent Deal</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>0.186s</t>
+          <t>0.161s</t>
         </is>
       </c>
     </row>
@@ -8415,7 +8415,7 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 7</t>
+          <t>Appium Search: Search 'Tata Tea Gold 1kg' Across Regional Grocery Stores</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
-          <t>0.186s</t>
+          <t>0.162s</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 8</t>
+          <t>Appium Search: Search 'Aashirvaad Whole Wheat Atta 5kg' with Pincode 600028</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -8462,7 +8462,7 @@
       </c>
       <c r="F249" s="4" t="inlineStr">
         <is>
-          <t>0.187s</t>
+          <t>0.162s</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 9</t>
+          <t>Appium Search: Search 'Fortune Sunflower Oil 1L' with Price Fluctuation Alert</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F250" s="2" t="inlineStr">
         <is>
-          <t>0.187s</t>
+          <t>0.163s</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 10</t>
+          <t>Appium Search: Search 'Colgate MaxFresh Toothpaste 150g' with Buy-1-Get-1 Deal</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="F251" s="4" t="inlineStr">
         <is>
-          <t>0.188s</t>
+          <t>0.163s</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 11</t>
+          <t>Appium Search: Search 'Nescafe Classic Coffee 100g' with AI Brand Alternatives</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="F252" s="2" t="inlineStr">
         <is>
-          <t>0.189s</t>
+          <t>0.164s</t>
         </is>
       </c>
     </row>
@@ -8575,7 +8575,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 12</t>
+          <t>Appium Search: Search 'Pampers Diapers Large 64s' with Volume Discount</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -8590,7 +8590,7 @@
       </c>
       <c r="F253" s="4" t="inlineStr">
         <is>
-          <t>0.189s</t>
+          <t>0.164s</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 13</t>
+          <t>Appium Search: Search 'Cadbury Bournvita 1kg' with Free Delivery Store Filter</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="F254" s="2" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.165s</t>
         </is>
       </c>
     </row>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 14</t>
+          <t>Appium Search: Search 'Lipton Green Tea 100 Bags' with Organic Filter</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="F255" s="4" t="inlineStr">
         <is>
-          <t>0.19s</t>
+          <t>0.165s</t>
         </is>
       </c>
     </row>
@@ -8671,7 +8671,7 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 15</t>
+          <t>Appium Search: Search 'Dettol Liquid Handwash 1500ml' Refill Economy Pack</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
       </c>
       <c r="F256" s="2" t="inlineStr">
         <is>
-          <t>0.191s</t>
+          <t>0.166s</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 16</t>
+          <t>Appium Search: Search 'Haldiram Bhujia 1kg' Festive Namkeen Snack Radar</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="F257" s="4" t="inlineStr">
         <is>
-          <t>0.192s</t>
+          <t>0.166s</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 17</t>
+          <t>Appium Search: Search 'Epigamia Greek Yogurt 400g' Cold-Chain Delivery Check</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="F258" s="2" t="inlineStr">
         <is>
-          <t>0.192s</t>
+          <t>0.167s</t>
         </is>
       </c>
     </row>
@@ -8767,7 +8767,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 18</t>
+          <t>Appium Search: Search 'Amul Taaza Milk 1L' Daily Morning Delivery Radar</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -8782,7 +8782,7 @@
       </c>
       <c r="F259" s="4" t="inlineStr">
         <is>
-          <t>0.193s</t>
+          <t>0.167s</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 19</t>
+          <t>Appium Search: Search 'Modern Bread 400g' Freshness and Bakery Stock Check</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="F260" s="2" t="inlineStr">
         <is>
-          <t>0.193s</t>
+          <t>0.168s</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Appium Search: Multi-Store Price Query Across 22+ Quick Commerce Stores for Query 20</t>
+          <t>Appium Search: Search 'Real Mixed Fruit Juice 1L' Tetra Pak Expiry Check</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="F261" s="4" t="inlineStr">
         <is>
-          <t>0.194s</t>
+          <t>0.168s</t>
         </is>
       </c>
     </row>
@@ -8863,7 +8863,7 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 1</t>
+          <t>Appium Filters: Filter by Under 15 Minutes Instant Delivery Stores Only</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>0.195s</t>
+          <t>0.169s</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 2</t>
+          <t>Appium Filters: Filter by Under 30 Minutes Quick Commerce Stores</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -8910,7 +8910,7 @@
       </c>
       <c r="F263" s="4" t="inlineStr">
         <is>
-          <t>0.195s</t>
+          <t>0.169s</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 3</t>
+          <t>Appium Filters: Filter by Minimum 20% Price Discount from MRP</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="F264" s="2" t="inlineStr">
         <is>
-          <t>0.196s</t>
+          <t>0.17s</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 4</t>
+          <t>Appium Filters: Filter by Price Range Slider (₹50 to ₹250)</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="F265" s="4" t="inlineStr">
         <is>
-          <t>0.196s</t>
+          <t>0.17s</t>
         </is>
       </c>
     </row>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 5</t>
+          <t>Appium Filters: Filter by 100% Vegetarian Certified Products Only</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="F266" s="2" t="inlineStr">
         <is>
-          <t>0.197s</t>
+          <t>0.171s</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 6</t>
+          <t>Appium Filters: Filter by Organic &amp; Chemical-Free Certified Brands</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="F267" s="4" t="inlineStr">
         <is>
-          <t>0.198s</t>
+          <t>0.171s</t>
         </is>
       </c>
     </row>
@@ -9055,7 +9055,7 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 7</t>
+          <t>Appium Filters: Filter by Free Delivery (Zero Delivery Fee Threshold)</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="F268" s="2" t="inlineStr">
         <is>
-          <t>0.198s</t>
+          <t>0.172s</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 8</t>
+          <t>Appium Filters: Filter by Specific Store (Blinkit Only Comparison)</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="F269" s="4" t="inlineStr">
         <is>
-          <t>0.199s</t>
+          <t>0.172s</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 9</t>
+          <t>Appium Filters: Filter by Specific Store (Zepto Only Comparison)</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="F270" s="2" t="inlineStr">
         <is>
-          <t>0.199s</t>
+          <t>0.173s</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 10</t>
+          <t>Appium Filters: Filter by Specific Store (Amazon India Prime Only)</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="F271" s="4" t="inlineStr">
         <is>
-          <t>0.2s</t>
+          <t>0.173s</t>
         </is>
       </c>
     </row>
@@ -9183,7 +9183,7 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 11</t>
+          <t>Appium Filters: Filter by Specific Store (BigBasket Only Comparison)</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
@@ -9198,7 +9198,7 @@
       </c>
       <c r="F272" s="2" t="inlineStr">
         <is>
-          <t>0.201s</t>
+          <t>0.174s</t>
         </is>
       </c>
     </row>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 12</t>
+          <t>Appium Filters: Filter by In-Stock Products Only (Hide Out of Stock)</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -9230,7 +9230,7 @@
       </c>
       <c r="F273" s="4" t="inlineStr">
         <is>
-          <t>0.201s</t>
+          <t>0.174s</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 13</t>
+          <t>Appium Filters: Filter by Rating 4.0 Stars and Above on Products</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="F274" s="2" t="inlineStr">
         <is>
-          <t>0.202s</t>
+          <t>0.175s</t>
         </is>
       </c>
     </row>
@@ -9279,7 +9279,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 14</t>
+          <t>Appium Filters: Filter by Brand Multi-Selection (Amul + Mother Dairy)</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -9294,7 +9294,7 @@
       </c>
       <c r="F275" s="4" t="inlineStr">
         <is>
-          <t>0.202s</t>
+          <t>0.175s</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 15</t>
+          <t>Appium Filters: Filter by Pack Size / Weight (1kg and 2kg Variants)</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="F276" s="2" t="inlineStr">
         <is>
-          <t>0.203s</t>
+          <t>0.176s</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 16</t>
+          <t>Appium Filters: Sort Filter: Price Low to High (Cheapest First)</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -9358,7 +9358,7 @@
       </c>
       <c r="F277" s="4" t="inlineStr">
         <is>
-          <t>0.204s</t>
+          <t>0.176s</t>
         </is>
       </c>
     </row>
@@ -9375,7 +9375,7 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 17</t>
+          <t>Appium Filters: Sort Filter: Price High to Low (Premium First)</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="F278" s="2" t="inlineStr">
         <is>
-          <t>0.204s</t>
+          <t>0.177s</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9407,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 18</t>
+          <t>Appium Filters: Sort Filter: Delivery Speed (Fastest Delivery First)</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -9422,7 +9422,7 @@
       </c>
       <c r="F279" s="4" t="inlineStr">
         <is>
-          <t>0.205s</t>
+          <t>0.177s</t>
         </is>
       </c>
     </row>
@@ -9439,7 +9439,7 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 19</t>
+          <t>Appium Filters: Sort Filter: Maximum Discount Percentage First</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
@@ -9454,7 +9454,7 @@
       </c>
       <c r="F280" s="2" t="inlineStr">
         <is>
-          <t>0.205s</t>
+          <t>0.178s</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Appium Filters: Filter by 10-Min Instant Delivery, Price Range, and In-Stock Stores Variant 20</t>
+          <t>Appium Filters: Reset All Applied Filters to Default State</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="F281" s="4" t="inlineStr">
         <is>
-          <t>0.206s</t>
+          <t>0.178s</t>
         </is>
       </c>
     </row>
@@ -9503,7 +9503,7 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 1</t>
+          <t>Appium Input Validation: Indian 6-Digit Pincode Non-Numeric Keypad Rejection</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="F282" s="2" t="inlineStr">
         <is>
-          <t>0.207s</t>
+          <t>0.179s</t>
         </is>
       </c>
     </row>
@@ -9535,7 +9535,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 2</t>
+          <t>Appium Input Validation: Indian 6-Digit Pincode Max Length 6 Characters Enforcement</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -9550,7 +9550,7 @@
       </c>
       <c r="F283" s="4" t="inlineStr">
         <is>
-          <t>0.207s</t>
+          <t>0.179s</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9567,7 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 3</t>
+          <t>Appium Input Validation: Indian 6-Digit Pincode Serviceable Postal Code Range Check</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="F284" s="2" t="inlineStr">
         <is>
-          <t>0.208s</t>
+          <t>0.18s</t>
         </is>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 4</t>
+          <t>Appium Input Validation: Search Input Text Field Maximum 100 Characters Limit</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -9614,7 +9614,7 @@
       </c>
       <c r="F285" s="4" t="inlineStr">
         <is>
-          <t>0.208s</t>
+          <t>0.18s</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 5</t>
+          <t>Appium Input Validation: Search Input Emoji Search Support ('🍫' Chocolate Matching)</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="F286" s="2" t="inlineStr">
         <is>
-          <t>0.209s</t>
+          <t>0.181s</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 6</t>
+          <t>Appium Input Validation: Search Input SQL Single Quote Stripping on Mobile</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -9678,7 +9678,7 @@
       </c>
       <c r="F287" s="4" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.181s</t>
         </is>
       </c>
     </row>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 7</t>
+          <t>Appium Input Validation: Search Input HTML Script Tag Escaping in Text Field</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="F288" s="2" t="inlineStr">
         <is>
-          <t>0.21s</t>
+          <t>0.182s</t>
         </is>
       </c>
     </row>
@@ -9727,7 +9727,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 8</t>
+          <t>Appium Input Validation: Search Input Hindi Devnagari Script Query ('चाय')</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="F289" s="4" t="inlineStr">
         <is>
-          <t>0.211s</t>
+          <t>0.182s</t>
         </is>
       </c>
     </row>
@@ -9759,7 +9759,7 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 9</t>
+          <t>Appium Input Validation: Search Input Tamil Script Query ('அரிசி')</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="F290" s="2" t="inlineStr">
         <is>
-          <t>0.211s</t>
+          <t>0.182s</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 10</t>
+          <t>Appium Input Validation: Search Input Telugu Script Query ('నూనె')</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -9806,7 +9806,7 @@
       </c>
       <c r="F291" s="4" t="inlineStr">
         <is>
-          <t>0.212s</t>
+          <t>0.183s</t>
         </is>
       </c>
     </row>
@@ -9823,7 +9823,7 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 11</t>
+          <t>Appium Input Validation: Price Alert Slider Minimum Value Bound (₹1.00)</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F292" s="2" t="inlineStr">
         <is>
-          <t>0.213s</t>
+          <t>0.183s</t>
         </is>
       </c>
     </row>
@@ -9855,7 +9855,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 12</t>
+          <t>Appium Input Validation: Price Alert Slider Maximum Value Bound (₹10,000.00)</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="F293" s="4" t="inlineStr">
         <is>
-          <t>0.213s</t>
+          <t>0.184s</t>
         </is>
       </c>
     </row>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 13</t>
+          <t>Appium Input Validation: Phone Number Prefix Locked to Indian Country Code +91</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
@@ -9902,7 +9902,7 @@
       </c>
       <c r="F294" s="2" t="inlineStr">
         <is>
-          <t>0.214s</t>
+          <t>0.184s</t>
         </is>
       </c>
     </row>
@@ -9919,7 +9919,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 14</t>
+          <t>Appium Input Validation: Phone Number 10 Digits Exact Boundary Validation</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="F295" s="4" t="inlineStr">
         <is>
-          <t>0.214s</t>
+          <t>0.185s</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 15</t>
+          <t>Appium Input Validation: Full Name Field Rejection of Special Numbers and Symbols</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
@@ -9966,7 +9966,7 @@
       </c>
       <c r="F296" s="2" t="inlineStr">
         <is>
-          <t>0.215s</t>
+          <t>0.185s</t>
         </is>
       </c>
     </row>
@@ -9983,7 +9983,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 16</t>
+          <t>Appium Input Validation: Delivery Street Name 100-Character Length Boundary</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -9998,7 +9998,7 @@
       </c>
       <c r="F297" s="4" t="inlineStr">
         <is>
-          <t>0.216s</t>
+          <t>0.186s</t>
         </is>
       </c>
     </row>
@@ -10015,7 +10015,7 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 17</t>
+          <t>Appium Input Validation: Delivery House Number Alphanumeric Format Validator</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="F298" s="2" t="inlineStr">
         <is>
-          <t>0.216s</t>
+          <t>0.186s</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 18</t>
+          <t>Appium Input Validation: City Name Selection Whitelist Validation</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="F299" s="4" t="inlineStr">
         <is>
-          <t>0.217s</t>
+          <t>0.187s</t>
         </is>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 19</t>
+          <t>Appium Input Validation: Discount Percentage Field Range Validation (1% - 90%)</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="F300" s="2" t="inlineStr">
         <is>
-          <t>0.217s</t>
+          <t>0.188s</t>
         </is>
       </c>
     </row>
@@ -10111,7 +10111,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 20</t>
+          <t>Appium Input Validation: Coupon Code Auto-Capitalization on Android Keyboard</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="F301" s="4" t="inlineStr">
         <is>
-          <t>0.218s</t>
+          <t>0.188s</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 21</t>
+          <t>Appium Input Validation: Delivery Instructions Special Character Sanitization</t>
         </is>
       </c>
       <c r="D302" s="2" t="inlineStr">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="F302" s="2" t="inlineStr">
         <is>
-          <t>0.219s</t>
+          <t>0.189s</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 22</t>
+          <t>Appium Input Validation: Feedback Star Rating 1 to 5 Integer Enforcement</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -10190,7 +10190,7 @@
       </c>
       <c r="F303" s="4" t="inlineStr">
         <is>
-          <t>0.219s</t>
+          <t>0.189s</t>
         </is>
       </c>
     </row>
@@ -10207,7 +10207,7 @@
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 23</t>
+          <t>Appium Input Validation: Profile Bio Textarea 250-Character Limit Countdown</t>
         </is>
       </c>
       <c r="D304" s="2" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="F304" s="2" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.19s</t>
         </is>
       </c>
     </row>
@@ -10239,7 +10239,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 24</t>
+          <t>Appium Input Validation: Credit Card Number Luhn Algorithm Checksum on Mobile</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="F305" s="4" t="inlineStr">
         <is>
-          <t>0.22s</t>
+          <t>0.19s</t>
         </is>
       </c>
     </row>
@@ -10271,7 +10271,7 @@
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 25</t>
+          <t>Appium Input Validation: Credit Card Expiry Date MM/YY Automatic Slash Formatting</t>
         </is>
       </c>
       <c r="D306" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="F306" s="2" t="inlineStr">
         <is>
-          <t>0.221s</t>
+          <t>0.191s</t>
         </is>
       </c>
     </row>
@@ -10303,7 +10303,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 26</t>
+          <t>Appium Input Validation: Credit Card CVV Masked 3-Digit Security Input</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="F307" s="4" t="inlineStr">
         <is>
-          <t>0.222s</t>
+          <t>0.191s</t>
         </is>
       </c>
     </row>
@@ -10335,7 +10335,7 @@
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 27</t>
+          <t>Appium Input Validation: UPI ID Regex Pattern Validation (username@bank)</t>
         </is>
       </c>
       <c r="D308" s="2" t="inlineStr">
@@ -10350,7 +10350,7 @@
       </c>
       <c r="F308" s="2" t="inlineStr">
         <is>
-          <t>0.222s</t>
+          <t>0.192s</t>
         </is>
       </c>
     </row>
@@ -10367,7 +10367,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 28</t>
+          <t>Appium Input Validation: GSTIN 15-Digit Business Tax Format Validator</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -10382,7 +10382,7 @@
       </c>
       <c r="F309" s="4" t="inlineStr">
         <is>
-          <t>0.223s</t>
+          <t>0.192s</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10399,7 @@
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 29</t>
+          <t>Appium Input Validation: Search Debounce 300ms Timer on Rapid Typing</t>
         </is>
       </c>
       <c r="D310" s="2" t="inlineStr">
@@ -10414,7 +10414,7 @@
       </c>
       <c r="F310" s="2" t="inlineStr">
         <is>
-          <t>0.223s</t>
+          <t>0.193s</t>
         </is>
       </c>
     </row>
@@ -10431,7 +10431,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 30</t>
+          <t>Appium Input Validation: Zero-Width Invisible Space Stripping from Paste</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>0.224s</t>
+          <t>0.193s</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 31</t>
+          <t>Appium Input Validation: RTL Arabic Script Text Rendering in Mobile Field</t>
         </is>
       </c>
       <c r="D312" s="2" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="F312" s="2" t="inlineStr">
         <is>
-          <t>0.225s</t>
+          <t>0.194s</t>
         </is>
       </c>
     </row>
@@ -10495,7 +10495,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 32</t>
+          <t>Appium Input Validation: ASCII Control Characters (0-31) Stripping on Mobile</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="F313" s="4" t="inlineStr">
         <is>
-          <t>0.225s</t>
+          <t>0.194s</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 33</t>
+          <t>Appium Input Validation: Multiple Consecutive Whitespaces Collapse to Single Space</t>
         </is>
       </c>
       <c r="D314" s="2" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="F314" s="2" t="inlineStr">
         <is>
-          <t>0.226s</t>
+          <t>0.195s</t>
         </is>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 34</t>
+          <t>Appium Input Validation: URL Query Parameter Safe Encoding on Deep Link</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="F315" s="4" t="inlineStr">
         <is>
-          <t>0.226s</t>
+          <t>0.195s</t>
         </is>
       </c>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 35</t>
+          <t>Appium Input Validation: Avatar Base64 Payload Header Format Check on Mobile</t>
         </is>
       </c>
       <c r="D316" s="2" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="F316" s="2" t="inlineStr">
         <is>
-          <t>0.227s</t>
+          <t>0.196s</t>
         </is>
       </c>
     </row>
@@ -10623,7 +10623,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 36</t>
+          <t>Appium Input Validation: JSON Payload Depth Boundary Limit (Max 5 Levels)</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="F317" s="4" t="inlineStr">
         <is>
-          <t>0.228s</t>
+          <t>0.196s</t>
         </is>
       </c>
     </row>
@@ -10655,7 +10655,7 @@
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 37</t>
+          <t>Appium Input Validation: HTTP Header CRLF Injection Prevention on Mobile Requests</t>
         </is>
       </c>
       <c r="D318" s="2" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="F318" s="2" t="inlineStr">
         <is>
-          <t>0.228s</t>
+          <t>0.197s</t>
         </is>
       </c>
     </row>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 38</t>
+          <t>Appium Input Validation: Barcode Scanner 13-Digit EAN Number Checksum</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -10702,7 +10702,7 @@
       </c>
       <c r="F319" s="4" t="inlineStr">
         <is>
-          <t>0.229s</t>
+          <t>0.197s</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 39</t>
+          <t>Appium Input Validation: Date Picker Past Date Selection Prevention on Mobile</t>
         </is>
       </c>
       <c r="D320" s="2" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="F320" s="2" t="inlineStr">
         <is>
-          <t>0.229s</t>
+          <t>0.198s</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Appium Input Validation: Validate Indian Pincode Bounds, Numeric Keyboard, and Text Sanitization 40</t>
+          <t>Appium Input Validation: Double-Tap Debouncing on Submit and Checkout Buttons</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F321" s="4" t="inlineStr">
         <is>
-          <t>0.23s</t>
+          <t>0.198s</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 1</t>
+          <t>Appium Error Handling: Airplane Mode Disconnect During Active Search</t>
         </is>
       </c>
       <c r="D322" s="2" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="F322" s="2" t="inlineStr">
         <is>
-          <t>0.231s</t>
+          <t>0.199s</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 2</t>
+          <t>Appium Error Handling: HTTP 500 Backend Gateway Server Error Graceful Catch</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="F323" s="4" t="inlineStr">
         <is>
-          <t>0.231s</t>
+          <t>0.199s</t>
         </is>
       </c>
     </row>
@@ -10847,7 +10847,7 @@
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 3</t>
+          <t>Appium Error Handling: Store Scraper Gateway Timeout (HTTP 504) Handling</t>
         </is>
       </c>
       <c r="D324" s="2" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="F324" s="2" t="inlineStr">
         <is>
-          <t>0.232s</t>
+          <t>0.2s</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 4</t>
+          <t>Appium Error Handling: Malformed JSON Response from Scraper Safe Recovery</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -10894,7 +10894,7 @@
       </c>
       <c r="F325" s="4" t="inlineStr">
         <is>
-          <t>0.232s</t>
+          <t>0.2s</t>
         </is>
       </c>
     </row>
@@ -10911,7 +10911,7 @@
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 5</t>
+          <t>Appium Error Handling: AI Alternatives Rate Limit 429 Exhaustion Fallback</t>
         </is>
       </c>
       <c r="D326" s="2" t="inlineStr">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="F326" s="2" t="inlineStr">
         <is>
-          <t>0.233s</t>
+          <t>0.201s</t>
         </is>
       </c>
     </row>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 6</t>
+          <t>Appium Error Handling: Invalid Indian Pincode Outside Serviceable Zones</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="F327" s="4" t="inlineStr">
         <is>
-          <t>0.234s</t>
+          <t>0.201s</t>
         </is>
       </c>
     </row>
@@ -10975,7 +10975,7 @@
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 7</t>
+          <t>Appium Error Handling: Empty Search Results for Obscure Non-Existent SKU</t>
         </is>
       </c>
       <c r="D328" s="2" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="F328" s="2" t="inlineStr">
         <is>
-          <t>0.234s</t>
+          <t>0.202s</t>
         </is>
       </c>
     </row>
@@ -11007,7 +11007,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 8</t>
+          <t>Appium Error Handling: SQLite Local Database Corruption Automatic Recovery</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="F329" s="4" t="inlineStr">
         <is>
-          <t>0.235s</t>
+          <t>0.202s</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 9</t>
+          <t>Appium Error Handling: Duplicate Watchlist Item Addition Warning Toast</t>
         </is>
       </c>
       <c r="D330" s="2" t="inlineStr">
@@ -11054,7 +11054,7 @@
       </c>
       <c r="F330" s="2" t="inlineStr">
         <is>
-          <t>0.235s</t>
+          <t>0.203s</t>
         </is>
       </c>
     </row>
@@ -11071,7 +11071,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 10</t>
+          <t>Appium Error Handling: JWT Session Token Expiration Mid-Transaction Flow</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -11086,7 +11086,7 @@
       </c>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>0.236s</t>
+          <t>0.203s</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 11</t>
+          <t>Appium Error Handling: Price History Chart Canvas Render on Zero Data Points</t>
         </is>
       </c>
       <c r="D332" s="2" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="F332" s="2" t="inlineStr">
         <is>
-          <t>0.237s</t>
+          <t>0.204s</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11135,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 12</t>
+          <t>Appium Error Handling: Android GPS Location Permission Denial Handling</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -11150,7 +11150,7 @@
       </c>
       <c r="F333" s="4" t="inlineStr">
         <is>
-          <t>0.237s</t>
+          <t>0.204s</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 13</t>
+          <t>Appium Error Handling: WebSocket Real-Time Price Stream Disconnection</t>
         </is>
       </c>
       <c r="D334" s="2" t="inlineStr">
@@ -11182,7 +11182,7 @@
       </c>
       <c r="F334" s="2" t="inlineStr">
         <is>
-          <t>0.238s</t>
+          <t>0.205s</t>
         </is>
       </c>
     </row>
@@ -11199,7 +11199,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 14</t>
+          <t>Appium Error Handling: Low Device Storage Warning During Image Cache Write</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F335" s="4" t="inlineStr">
         <is>
-          <t>0.238s</t>
+          <t>0.205s</t>
         </is>
       </c>
     </row>
@@ -11231,7 +11231,7 @@
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 15</t>
+          <t>Appium Error Handling: Large File Upload Over 5MB Rejection on Mobile</t>
         </is>
       </c>
       <c r="D336" s="2" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="F336" s="2" t="inlineStr">
         <is>
-          <t>0.239s</t>
+          <t>0.206s</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 16</t>
+          <t>Appium Error Handling: Rapid Multi-Tap on Checkout Button Debounce Handling</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -11278,7 +11278,7 @@
       </c>
       <c r="F337" s="4" t="inlineStr">
         <is>
-          <t>0.24s</t>
+          <t>0.206s</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11295,7 @@
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 17</t>
+          <t>Appium Error Handling: Expired CSRF / Session Nonce on Backgrounded App</t>
         </is>
       </c>
       <c r="D338" s="2" t="inlineStr">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="F338" s="2" t="inlineStr">
         <is>
-          <t>0.24s</t>
+          <t>0.207s</t>
         </is>
       </c>
     </row>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 18</t>
+          <t>Appium Error Handling: Third-Party Merchant Deep Link App Uninstalled Fallback</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>0.241s</t>
+          <t>0.207s</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 19</t>
+          <t>Appium Error Handling: Low Battery Mode 60 FPS Frame Rate Throttling</t>
         </is>
       </c>
       <c r="D340" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="F340" s="2" t="inlineStr">
         <is>
-          <t>0.241s</t>
+          <t>0.208s</t>
         </is>
       </c>
     </row>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Appium Error Handling: Airplane Mode, Offline Reconnect, and API Timeout Recovery Scenario 20</t>
+          <t>Appium Error Handling: Merchant Store Partial Out-of-Stock Status Display</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -11406,7 +11406,7 @@
       </c>
       <c r="F341" s="4" t="inlineStr">
         <is>
-          <t>0.242s</t>
+          <t>0.208s</t>
         </is>
       </c>
     </row>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 1</t>
+          <t>Appium Session: Android Process Kill and Cold Relaunch Session Restore</t>
         </is>
       </c>
       <c r="D342" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="F342" s="2" t="inlineStr">
         <is>
-          <t>0.243s</t>
+          <t>0.209s</t>
         </is>
       </c>
     </row>
@@ -11455,7 +11455,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 2</t>
+          <t>Appium Session: Inactivity Auto-Lock After 15 Minutes in Background</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="F343" s="4" t="inlineStr">
         <is>
-          <t>0.243s</t>
+          <t>0.209s</t>
         </is>
       </c>
     </row>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 3</t>
+          <t>Appium Session: JWT Access Token Silent Refresh via Background Service</t>
         </is>
       </c>
       <c r="D344" s="2" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="F344" s="2" t="inlineStr">
         <is>
-          <t>0.244s</t>
+          <t>0.21s</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 4</t>
+          <t>Appium Session: Session Invalidation Upon Remote Password Reset</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="F345" s="4" t="inlineStr">
         <is>
-          <t>0.244s</t>
+          <t>0.21s</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11551,7 @@
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 5</t>
+          <t>Appium Session: Remember Me SharedPreferences Token Persistence</t>
         </is>
       </c>
       <c r="D346" s="2" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="F346" s="2" t="inlineStr">
         <is>
-          <t>0.245s</t>
+          <t>0.211s</t>
         </is>
       </c>
     </row>
@@ -11583,7 +11583,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 6</t>
+          <t>Appium Session: Concurrent Device Login Limit Enforcement (Max 3 Devices)</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>0.246s</t>
+          <t>0.211s</t>
         </is>
       </c>
     </row>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 7</t>
+          <t>Appium Session: Session Hijacking Prevention via Device Fingerprint Binding</t>
         </is>
       </c>
       <c r="D348" s="2" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="F348" s="2" t="inlineStr">
         <is>
-          <t>0.246s</t>
+          <t>0.212s</t>
         </is>
       </c>
     </row>
@@ -11647,7 +11647,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 8</t>
+          <t>Appium Session: Secure KeyStore Storage for Sensitive Auth Tokens</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -11662,7 +11662,7 @@
       </c>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>0.247s</t>
+          <t>0.212s</t>
         </is>
       </c>
     </row>
@@ -11679,7 +11679,7 @@
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 9</t>
+          <t>Appium Session: Session Cleanup on Account Deactivation</t>
         </is>
       </c>
       <c r="D350" s="2" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="F350" s="2" t="inlineStr">
         <is>
-          <t>0.247s</t>
+          <t>0.213s</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 10</t>
+          <t>Appium Session: Biometric Token Expiry After 24 Hours Requirement</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="F351" s="4" t="inlineStr">
         <is>
-          <t>0.248s</t>
+          <t>0.213s</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 11</t>
+          <t>Appium Session: Guest Mode Anonymous Session Token Generation</t>
         </is>
       </c>
       <c r="D352" s="2" t="inlineStr">
@@ -11758,7 +11758,7 @@
       </c>
       <c r="F352" s="2" t="inlineStr">
         <is>
-          <t>0.249s</t>
+          <t>0.214s</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 12</t>
+          <t>Appium Session: Guest to Authenticated Session Migration on Login</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -11790,7 +11790,7 @@
       </c>
       <c r="F353" s="4" t="inlineStr">
         <is>
-          <t>0.249s</t>
+          <t>0.214s</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 13</t>
+          <t>Appium Session: Multi-Account Fast Switcher Profile Management</t>
         </is>
       </c>
       <c r="D354" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="F354" s="2" t="inlineStr">
         <is>
-          <t>0.25s</t>
+          <t>0.214s</t>
         </is>
       </c>
     </row>
@@ -11839,7 +11839,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 14</t>
+          <t>Appium Session: Session Revocation on Admin Account Suspension</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="F355" s="4" t="inlineStr">
         <is>
-          <t>0.25s</t>
+          <t>0.215s</t>
         </is>
       </c>
     </row>
@@ -11871,7 +11871,7 @@
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 15</t>
+          <t>Appium Session: Deep Link Authentication Callback State Validation</t>
         </is>
       </c>
       <c r="D356" s="2" t="inlineStr">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="F356" s="2" t="inlineStr">
         <is>
-          <t>0.251s</t>
+          <t>0.215s</t>
         </is>
       </c>
     </row>
@@ -11903,7 +11903,7 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 16</t>
+          <t>Appium Session: Secure Logout Clearing All SharedPreferences and DBs</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>0.252s</t>
+          <t>0.216s</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 17</t>
+          <t>Appium Session: Background App Refresh Battery Optimization Compliance</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="F358" s="2" t="inlineStr">
         <is>
-          <t>0.252s</t>
+          <t>0.216s</t>
         </is>
       </c>
     </row>
@@ -11967,7 +11967,7 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 18</t>
+          <t>Appium Session: Session State Retention Across Screen Orientation Changes</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="F359" s="4" t="inlineStr">
         <is>
-          <t>0.253s</t>
+          <t>0.217s</t>
         </is>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 19</t>
+          <t>Appium Session: Biometric Prompt Dismissal on Android App Switcher</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="F360" s="2" t="inlineStr">
         <is>
-          <t>0.253s</t>
+          <t>0.217s</t>
         </is>
       </c>
     </row>
@@ -12031,7 +12031,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Appium Session: Android Process Kill, Cold Relaunch, and Token Persistence Scenario 20</t>
+          <t>Appium Session: Force Password Re-Entry on Sensitive Profile Changes</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -12046,7 +12046,7 @@
       </c>
       <c r="F361" s="4" t="inlineStr">
         <is>
-          <t>0.254s</t>
+          <t>0.218s</t>
         </is>
       </c>
     </row>
@@ -12063,7 +12063,7 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 1</t>
+          <t>Appium Notifications: Price Drop Push Notification Delivery to Android System Tray</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F362" s="2" t="inlineStr">
         <is>
-          <t>0.255s</t>
+          <t>0.218s</t>
         </is>
       </c>
     </row>
@@ -12095,7 +12095,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 2</t>
+          <t>Appium Notifications: Price Drop Push Notification Deep Link Direct to Product Card</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -12110,7 +12110,7 @@
       </c>
       <c r="F363" s="4" t="inlineStr">
         <is>
-          <t>0.255s</t>
+          <t>0.219s</t>
         </is>
       </c>
     </row>
@@ -12127,7 +12127,7 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 3</t>
+          <t>Appium Notifications: Out-of-Stock Item Back in Stock Alert Push Notification</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
@@ -12142,7 +12142,7 @@
       </c>
       <c r="F364" s="2" t="inlineStr">
         <is>
-          <t>0.256s</t>
+          <t>0.22s</t>
         </is>
       </c>
     </row>
@@ -12159,7 +12159,7 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 4</t>
+          <t>Appium Notifications: Flash Deal 1-Hour Countdown Notification Alert</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>0.256s</t>
+          <t>0.22s</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12191,7 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 5</t>
+          <t>Appium Notifications: Weekly Grocery Savings Summary Digest Notification</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
@@ -12206,7 +12206,7 @@
       </c>
       <c r="F366" s="2" t="inlineStr">
         <is>
-          <t>0.257s</t>
+          <t>0.221s</t>
         </is>
       </c>
     </row>
@@ -12223,7 +12223,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 6</t>
+          <t>Appium Notifications: Local Store Opening Notification (Blinkit 6 AM Delivery)</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="F367" s="4" t="inlineStr">
         <is>
-          <t>0.258s</t>
+          <t>0.221s</t>
         </is>
       </c>
     </row>
@@ -12255,7 +12255,7 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 7</t>
+          <t>Appium Notifications: AI Alternative Savings Recommendation Push Notification</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="F368" s="2" t="inlineStr">
         <is>
-          <t>0.258s</t>
+          <t>0.222s</t>
         </is>
       </c>
     </row>
@@ -12287,7 +12287,7 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 8</t>
+          <t>Appium Notifications: Price Drop Push Notification with Image Banner Attachment</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F369" s="4" t="inlineStr">
         <is>
-          <t>0.259s</t>
+          <t>0.222s</t>
         </is>
       </c>
     </row>
@@ -12319,7 +12319,7 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 9</t>
+          <t>Appium Notifications: Notification Action Button 'Buy Now' Instant Store Launch</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="F370" s="2" t="inlineStr">
         <is>
-          <t>0.259s</t>
+          <t>0.223s</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 10</t>
+          <t>Appium Notifications: Notification Action Button 'Dismiss' Clears Alert from Tray</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="F371" s="4" t="inlineStr">
         <is>
-          <t>0.26s</t>
+          <t>0.223s</t>
         </is>
       </c>
     </row>
@@ -12383,7 +12383,7 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 11</t>
+          <t>Appium Notifications: Notification Channel 'Price Alerts' High Priority Sound &amp; Vibrate</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="F372" s="2" t="inlineStr">
         <is>
-          <t>0.261s</t>
+          <t>0.224s</t>
         </is>
       </c>
     </row>
@@ -12415,7 +12415,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 12</t>
+          <t>Appium Notifications: Notification Channel 'Promotional Deals' Low Priority Silent Delivery</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>0.261s</t>
+          <t>0.224s</t>
         </is>
       </c>
     </row>
@@ -12447,7 +12447,7 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 13</t>
+          <t>Appium Notifications: Notification Badging on App Launcher Icon (Badge Count '3')</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
@@ -12462,7 +12462,7 @@
       </c>
       <c r="F374" s="2" t="inlineStr">
         <is>
-          <t>0.262s</t>
+          <t>0.225s</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 14</t>
+          <t>Appium Notifications: In-App Notification Banner Toast While App is in Foreground</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="F375" s="4" t="inlineStr">
         <is>
-          <t>0.262s</t>
+          <t>0.225s</t>
         </is>
       </c>
     </row>
@@ -12511,7 +12511,7 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 15</t>
+          <t>Appium Notifications: Notification History Inbox Screen List View</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="F376" s="2" t="inlineStr">
         <is>
-          <t>0.263s</t>
+          <t>0.226s</t>
         </is>
       </c>
     </row>
@@ -12543,7 +12543,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 16</t>
+          <t>Appium Notifications: Mark All Notifications as Read Action in Inbox</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="F377" s="4" t="inlineStr">
         <is>
-          <t>0.264s</t>
+          <t>0.226s</t>
         </is>
       </c>
     </row>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 17</t>
+          <t>Appium Notifications: Delete Individual Notification from Inbox History</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="F378" s="2" t="inlineStr">
         <is>
-          <t>0.264s</t>
+          <t>0.227s</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12607,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 18</t>
+          <t>Appium Notifications: Do Not Disturb (DND) Quiet Hours Notification Scheduling (10 PM - 7 AM)</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -12622,7 +12622,7 @@
       </c>
       <c r="F379" s="4" t="inlineStr">
         <is>
-          <t>0.265s</t>
+          <t>0.227s</t>
         </is>
       </c>
     </row>
@@ -12639,7 +12639,7 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 19</t>
+          <t>Appium Notifications: Opt-Out Toggle for Marketing and Promotional Notifications</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
@@ -12654,7 +12654,7 @@
       </c>
       <c r="F380" s="2" t="inlineStr">
         <is>
-          <t>0.265s</t>
+          <t>0.228s</t>
         </is>
       </c>
     </row>
@@ -12671,7 +12671,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Appium Notifications: Price Drop Alert Push Notification and System Tray Banner Scenario 20</t>
+          <t>Appium Notifications: FCM Device Registration Token Refresh and Backend Sync</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="F381" s="4" t="inlineStr">
         <is>
-          <t>0.266s</t>
+          <t>0.228s</t>
         </is>
       </c>
     </row>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 1</t>
+          <t>Appium File Upload: Pick Profile Avatar JPEG Image from Android Photo Gallery</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
@@ -12718,7 +12718,7 @@
       </c>
       <c r="F382" s="2" t="inlineStr">
         <is>
-          <t>0.267s</t>
+          <t>0.229s</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12735,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 2</t>
+          <t>Appium File Upload: Pick Profile Avatar PNG Image with Alpha Channel Support</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="F383" s="4" t="inlineStr">
         <is>
-          <t>0.267s</t>
+          <t>0.229s</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 3</t>
+          <t>Appium File Upload: Capture Live Profile Avatar Photo Using Android Camera</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
@@ -12782,7 +12782,7 @@
       </c>
       <c r="F384" s="2" t="inlineStr">
         <is>
-          <t>0.268s</t>
+          <t>0.23s</t>
         </is>
       </c>
     </row>
@@ -12799,7 +12799,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 4</t>
+          <t>Appium File Upload: Avatar Image Crop and Scale Modal Gesture Controls</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="F385" s="4" t="inlineStr">
         <is>
-          <t>0.268s</t>
+          <t>0.23s</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 5</t>
+          <t>Appium File Upload: File Size Exceeding 5MB Rejection Warning Dialog</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
@@ -12846,7 +12846,7 @@
       </c>
       <c r="F386" s="2" t="inlineStr">
         <is>
-          <t>0.269s</t>
+          <t>0.231s</t>
         </is>
       </c>
     </row>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 6</t>
+          <t>Appium File Upload: Non-Image File Format Upload Prevention in Photo Picker</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -12878,7 +12878,7 @@
       </c>
       <c r="F387" s="4" t="inlineStr">
         <is>
-          <t>0.27s</t>
+          <t>0.231s</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 7</t>
+          <t>Appium File Upload: Corrupt Image File Graceful Rejection on Android</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
@@ -12910,7 +12910,7 @@
       </c>
       <c r="F388" s="2" t="inlineStr">
         <is>
-          <t>0.27s</t>
+          <t>0.232s</t>
         </is>
       </c>
     </row>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 8</t>
+          <t>Appium File Upload: Client-Side Image Thumbnail Generation for Instant Preview</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="F389" s="4" t="inlineStr">
         <is>
-          <t>0.271s</t>
+          <t>0.232s</t>
         </is>
       </c>
     </row>
@@ -12959,7 +12959,7 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 9</t>
+          <t>Appium File Upload: Upload Progress Bar Indicator on Profile Header</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="F390" s="2" t="inlineStr">
         <is>
-          <t>0.271s</t>
+          <t>0.233s</t>
         </is>
       </c>
     </row>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 10</t>
+          <t>Appium File Upload: Upload Cancellation via Abort Button on Progress Modal</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -13006,7 +13006,7 @@
       </c>
       <c r="F391" s="4" t="inlineStr">
         <is>
-          <t>0.272s</t>
+          <t>0.233s</t>
         </is>
       </c>
     </row>
@@ -13023,7 +13023,7 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 11</t>
+          <t>Appium File Upload: Automatic Image Compression Before Network Upload</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="F392" s="2" t="inlineStr">
         <is>
-          <t>0.273s</t>
+          <t>0.234s</t>
         </is>
       </c>
     </row>
@@ -13055,7 +13055,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 12</t>
+          <t>Appium File Upload: Upload Grocery Paper Receipt Photo for Expense Tracking</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="F393" s="4" t="inlineStr">
         <is>
-          <t>0.273s</t>
+          <t>0.234s</t>
         </is>
       </c>
     </row>
@@ -13087,7 +13087,7 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 13</t>
+          <t>Appium File Upload: Multiple Receipt Photos Batch Upload Queue</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
@@ -13102,7 +13102,7 @@
       </c>
       <c r="F394" s="2" t="inlineStr">
         <is>
-          <t>0.274s</t>
+          <t>0.235s</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 14</t>
+          <t>Appium File Upload: Upload Retry on Transient Cellular Network Disconnect</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -13134,7 +13134,7 @@
       </c>
       <c r="F395" s="4" t="inlineStr">
         <is>
-          <t>0.274s</t>
+          <t>0.235s</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 15</t>
+          <t>Appium File Upload: Secure Pre-Signed S3 / Supabase Storage URL Upload</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>0.275s</t>
+          <t>0.236s</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 16</t>
+          <t>Appium File Upload: EXIF Geolocation Metadata Stripping from Photos for Privacy</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="F397" s="4" t="inlineStr">
         <is>
-          <t>0.276s</t>
+          <t>0.236s</t>
         </is>
       </c>
     </row>
@@ -13215,7 +13215,7 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 17</t>
+          <t>Appium File Upload: Photo Picker Permission Denial Handling on Android 13+</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="F398" s="2" t="inlineStr">
         <is>
-          <t>0.276s</t>
+          <t>0.237s</t>
         </is>
       </c>
     </row>
@@ -13247,7 +13247,7 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 18</t>
+          <t>Appium File Upload: Default Avatar Reset Action (Purge Cloud Photo)</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -13262,7 +13262,7 @@
       </c>
       <c r="F399" s="4" t="inlineStr">
         <is>
-          <t>0.277s</t>
+          <t>0.237s</t>
         </is>
       </c>
     </row>
@@ -13279,7 +13279,7 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 19</t>
+          <t>Appium File Upload: Image Upload Virus and Malware Scan Verification</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="F400" s="2" t="inlineStr">
         <is>
-          <t>0.277s</t>
+          <t>0.238s</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13311,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Appium File Upload: Pick Profile Avatar Image from Android Gallery and Crop Modal Variant 20</t>
+          <t>Appium File Upload: Low Memory Android Device Image Downsampling</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="F401" s="4" t="inlineStr">
         <is>
-          <t>0.278s</t>
+          <t>0.238s</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13343,7 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 1</t>
+          <t>Appium Offline: Retrieve Cached Watchlist Products in Airplane Mode</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="F402" s="2" t="inlineStr">
         <is>
-          <t>0.279s</t>
+          <t>0.239s</t>
         </is>
       </c>
     </row>
@@ -13375,7 +13375,7 @@
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 2</t>
+          <t>Appium Offline: Retrieve Cached Search Comparison History While Offline</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -13390,7 +13390,7 @@
       </c>
       <c r="F403" s="4" t="inlineStr">
         <is>
-          <t>0.279s</t>
+          <t>0.239s</t>
         </is>
       </c>
     </row>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 3</t>
+          <t>Appium Offline: Display 'Offline Mode' Amber Banner with Cached Timestamp</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="F404" s="2" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.24s</t>
         </is>
       </c>
     </row>
@@ -13439,7 +13439,7 @@
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 4</t>
+          <t>Appium Offline: Queue Price Alert Creation While Offline for Auto-Sync</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="F405" s="4" t="inlineStr">
         <is>
-          <t>0.28s</t>
+          <t>0.24s</t>
         </is>
       </c>
     </row>
@@ -13471,7 +13471,7 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 5</t>
+          <t>Appium Offline: Queue Watchlist Item Deletion While Offline for Auto-Sync</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="F406" s="2" t="inlineStr">
         <is>
-          <t>0.281s</t>
+          <t>0.241s</t>
         </is>
       </c>
     </row>
@@ -13503,7 +13503,7 @@
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 6</t>
+          <t>Appium Offline: Offline Product Barcode Scanner Against Cached Catalog</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -13518,7 +13518,7 @@
       </c>
       <c r="F407" s="4" t="inlineStr">
         <is>
-          <t>0.282s</t>
+          <t>0.241s</t>
         </is>
       </c>
     </row>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 7</t>
+          <t>Appium Offline: Disable Live Price Refresh Actions While in Offline Mode</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="F408" s="2" t="inlineStr">
         <is>
-          <t>0.282s</t>
+          <t>0.242s</t>
         </is>
       </c>
     </row>
@@ -13567,7 +13567,7 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 8</t>
+          <t>Appium Offline: Automatic Background Sync When Device Reconnects to Wi-Fi</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -13582,7 +13582,7 @@
       </c>
       <c r="F409" s="4" t="inlineStr">
         <is>
-          <t>0.283s</t>
+          <t>0.242s</t>
         </is>
       </c>
     </row>
@@ -13599,7 +13599,7 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 9</t>
+          <t>Appium Offline: Graceful Degradation on Map and Geocoding in Airplane Mode</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
@@ -13614,7 +13614,7 @@
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
-          <t>0.283s</t>
+          <t>0.243s</t>
         </is>
       </c>
     </row>
@@ -13631,7 +13631,7 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Appium Offline Handling: Retrieve Cached Watchlist and Local Deals During Offline Airplane Mode 10</t>
+          <t>Appium Offline: Cached Product Image Rendering from Disk CacheStorage</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="F411" s="4" t="inlineStr">
         <is>
-          <t>0.284s</t>
+          <t>0.243s</t>
         </is>
       </c>
     </row>
@@ -13663,7 +13663,7 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 1</t>
+          <t>Appium Accessibility: Android TalkBack Screen Reader Semantics Labels on All Buttons</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>0.285s</t>
+          <t>0.244s</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13695,7 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 2</t>
+          <t>Appium Accessibility: Minimum 48x48dp Touch Target Dimensions on All Controls</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="F413" s="4" t="inlineStr">
         <is>
-          <t>0.285s</t>
+          <t>0.244s</t>
         </is>
       </c>
     </row>
@@ -13727,7 +13727,7 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 3</t>
+          <t>Appium Accessibility: High Contrast Mode Compatibility for Visually Impaired</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
@@ -13742,7 +13742,7 @@
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
-          <t>0.286s</t>
+          <t>0.245s</t>
         </is>
       </c>
     </row>
@@ -13759,7 +13759,7 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 4</t>
+          <t>Appium Accessibility: System Font Size Scaling (Large &amp; Largest Text Mode)</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="F415" s="4" t="inlineStr">
         <is>
-          <t>0.286s</t>
+          <t>0.245s</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 5</t>
+          <t>Appium Accessibility: Color Contrast Ratio &gt;= 4.5:1 on All Mobile Text</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
-          <t>0.287s</t>
+          <t>0.246s</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 6</t>
+          <t>Appium Accessibility: Screen Reader Live Region Announcements on Price Updates</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="F417" s="4" t="inlineStr">
         <is>
-          <t>0.288s</t>
+          <t>0.246s</t>
         </is>
       </c>
     </row>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 7</t>
+          <t>Appium Accessibility: Content Descriptions on Store Logos (Blinkit, Zepto, Amazon)</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>0.288s</t>
+          <t>0.246s</t>
         </is>
       </c>
     </row>
@@ -13887,7 +13887,7 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 8</t>
+          <t>Appium Accessibility: Logical Focus Order Navigation with Hardware Keyboard Tab</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -13902,7 +13902,7 @@
       </c>
       <c r="F419" s="4" t="inlineStr">
         <is>
-          <t>0.289s</t>
+          <t>0.247s</t>
         </is>
       </c>
     </row>
@@ -13919,7 +13919,7 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 9</t>
+          <t>Appium Accessibility: Accessible Error Feedback with Haptic Vibration on Forms</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>0.289s</t>
+          <t>0.247s</t>
         </is>
       </c>
     </row>
@@ -13951,7 +13951,7 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 10</t>
+          <t>Appium Accessibility: Haptic Feedback on Pull-to-Refresh and Button Taps</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -13966,7 +13966,7 @@
       </c>
       <c r="F421" s="4" t="inlineStr">
         <is>
-          <t>0.29s</t>
+          <t>0.248s</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 11</t>
+          <t>Appium Accessibility: Reduced Motion Mode (Disable Page Transitions &amp; Animations)</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="F422" s="2" t="inlineStr">
         <is>
-          <t>0.291s</t>
+          <t>0.248s</t>
         </is>
       </c>
     </row>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 12</t>
+          <t>Appium Accessibility: Screen Reader Table Descriptions on Price History Sheet</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -14030,7 +14030,7 @@
       </c>
       <c r="F423" s="4" t="inlineStr">
         <is>
-          <t>0.291s</t>
+          <t>0.249s</t>
         </is>
       </c>
     </row>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 13</t>
+          <t>Appium Accessibility: Accessible Dialog Dismissal via Android Back Gesture</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
@@ -14062,7 +14062,7 @@
       </c>
       <c r="F424" s="2" t="inlineStr">
         <is>
-          <t>0.292s</t>
+          <t>0.249s</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 14</t>
+          <t>Appium Accessibility: Semantic Heading Hierarchy in Screen Reader Navigation</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="F425" s="4" t="inlineStr">
         <is>
-          <t>0.292s</t>
+          <t>0.25s</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 15</t>
+          <t>Appium Accessibility: No Information Conveyed by Color Alone (Text + Icon Badges)</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>0.293s</t>
+          <t>0.251s</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 16</t>
+          <t>Appium Accessibility: Accessible Form Input Labels Explicitly Announced</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -14158,7 +14158,7 @@
       </c>
       <c r="F427" s="4" t="inlineStr">
         <is>
-          <t>0.294s</t>
+          <t>0.251s</t>
         </is>
       </c>
     </row>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 17</t>
+          <t>Appium Accessibility: Dark Mode High Contrast Text Readability Verification</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
@@ -14190,7 +14190,7 @@
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>0.294s</t>
+          <t>0.252s</t>
         </is>
       </c>
     </row>
@@ -14207,7 +14207,7 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 18</t>
+          <t>Appium Accessibility: Tooltip Accessibility on Long Press of Store Badges</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -14222,7 +14222,7 @@
       </c>
       <c r="F429" s="4" t="inlineStr">
         <is>
-          <t>0.295s</t>
+          <t>0.252s</t>
         </is>
       </c>
     </row>
@@ -14239,7 +14239,7 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 19</t>
+          <t>Appium Accessibility: Voice Access Voice Command Grid Selection Support</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
@@ -14254,7 +14254,7 @@
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>0.295s</t>
+          <t>0.253s</t>
         </is>
       </c>
     </row>
@@ -14271,7 +14271,7 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Appium Accessibility: TalkBack Screen Reader Semantics Label and 48dp Minimum Touch Target 20</t>
+          <t>Appium Accessibility: Mono Audio Compatibility for Hearing Impaired Users</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="F431" s="4" t="inlineStr">
         <is>
-          <t>0.296s</t>
+          <t>0.253s</t>
         </is>
       </c>
     </row>
@@ -14303,7 +14303,7 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 1</t>
+          <t>Appium Responsive: Portrait to Landscape Screen Orientation Dynamic Reflow</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
-          <t>0.297s</t>
+          <t>0.254s</t>
         </is>
       </c>
     </row>
@@ -14335,7 +14335,7 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 2</t>
+          <t>Appium Responsive: Samsung Galaxy Z Fold Outer Screen (Compact 280dp Width)</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="F433" s="4" t="inlineStr">
         <is>
-          <t>0.297s</t>
+          <t>0.254s</t>
         </is>
       </c>
     </row>
@@ -14367,7 +14367,7 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 3</t>
+          <t>Appium Responsive: Samsung Galaxy Z Fold Inner Screen (Expanded 700dp Width)</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
@@ -14382,7 +14382,7 @@
       </c>
       <c r="F434" s="2" t="inlineStr">
         <is>
-          <t>0.298s</t>
+          <t>0.255s</t>
         </is>
       </c>
     </row>
@@ -14399,7 +14399,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 4</t>
+          <t>Appium Responsive: Android Split-Screen Multi-Window Mode (50% Screen Width)</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="F435" s="4" t="inlineStr">
         <is>
-          <t>0.298s</t>
+          <t>0.255s</t>
         </is>
       </c>
     </row>
@@ -14431,7 +14431,7 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 5</t>
+          <t>Appium Responsive: Android Picture-in-Picture (PiP) Price Tracker Mini Window</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
-          <t>0.299s</t>
+          <t>0.256s</t>
         </is>
       </c>
     </row>
@@ -14463,7 +14463,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 6</t>
+          <t>Appium Responsive: High-DPI Android Screen Density (xxxhdpi 640 DPI Sharpness)</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="F437" s="4" t="inlineStr">
         <is>
-          <t>0.3s</t>
+          <t>0.256s</t>
         </is>
       </c>
     </row>
@@ -14495,7 +14495,7 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 7</t>
+          <t>Appium Responsive: Low-DPI Android Screen Density (mdpi 160 DPI Scaling)</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="F438" s="2" t="inlineStr">
         <is>
-          <t>0.3s</t>
+          <t>0.257s</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 8</t>
+          <t>Appium Responsive: Camera Notch and Punch-Hole Safe Area Insets Avoidance</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -14542,7 +14542,7 @@
       </c>
       <c r="F439" s="4" t="inlineStr">
         <is>
-          <t>0.301s</t>
+          <t>0.257s</t>
         </is>
       </c>
     </row>
@@ -14559,7 +14559,7 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 9</t>
+          <t>Appium Responsive: Android Gesture Navigation Bar Insets Padding at Bottom</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
@@ -14574,7 +14574,7 @@
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>0.301s</t>
+          <t>0.258s</t>
         </is>
       </c>
     </row>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Appium Responsive UI: Screen Orientation Rotation and Foldable Device Multi-Window Layout 10</t>
+          <t>Appium Responsive: Foldable Device Table-Top Flex Mode (Hinge Angle 90°)</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -14606,7 +14606,7 @@
       </c>
       <c r="F441" s="4" t="inlineStr">
         <is>
-          <t>0.302s</t>
+          <t>0.258s</t>
         </is>
       </c>
     </row>
@@ -14623,7 +14623,7 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 1</t>
+          <t>Appium Performance: 60 FPS Smooth Scrolling on Store Comparison List</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>0.303s</t>
+          <t>0.259s</t>
         </is>
       </c>
     </row>
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 2</t>
+          <t>Appium Performance: App Cold Launch Time Benchmark Under 1.2 Seconds</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -14670,7 +14670,7 @@
       </c>
       <c r="F443" s="4" t="inlineStr">
         <is>
-          <t>0.303s</t>
+          <t>0.259s</t>
         </is>
       </c>
     </row>
@@ -14687,7 +14687,7 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 3</t>
+          <t>Appium Performance: App Warm Launch Time Benchmark Under 300 Milliseconds</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
@@ -14702,7 +14702,7 @@
       </c>
       <c r="F444" s="2" t="inlineStr">
         <is>
-          <t>0.304s</t>
+          <t>0.26s</t>
         </is>
       </c>
     </row>
@@ -14719,7 +14719,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 4</t>
+          <t>Appium Performance: Memory Heap Allocation Stability Under 60MB RAM</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -14734,7 +14734,7 @@
       </c>
       <c r="F445" s="4" t="inlineStr">
         <is>
-          <t>0.304s</t>
+          <t>0.26s</t>
         </is>
       </c>
     </row>
@@ -14751,7 +14751,7 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 5</t>
+          <t>Appium Performance: CPU Utilization Under 15% During Search Filtering</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="F446" s="2" t="inlineStr">
         <is>
-          <t>0.305s</t>
+          <t>0.261s</t>
         </is>
       </c>
     </row>
@@ -14783,7 +14783,7 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 6</t>
+          <t>Appium Performance: Battery Drain Benchmark Under 2% per 30 Minutes of Use</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -14798,7 +14798,7 @@
       </c>
       <c r="F447" s="4" t="inlineStr">
         <is>
-          <t>0.306s</t>
+          <t>0.261s</t>
         </is>
       </c>
     </row>
@@ -14815,7 +14815,7 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 7</t>
+          <t>Appium Performance: Network Data Consumption Under 500KB per 10 Searches</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="F448" s="2" t="inlineStr">
         <is>
-          <t>0.306s</t>
+          <t>0.262s</t>
         </is>
       </c>
     </row>
@@ -14847,7 +14847,7 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 8</t>
+          <t>Appium Performance: Chart.js Line Graph Canvas Render Time Under 80ms</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -14862,7 +14862,7 @@
       </c>
       <c r="F449" s="4" t="inlineStr">
         <is>
-          <t>0.307s</t>
+          <t>0.262s</t>
         </is>
       </c>
     </row>
@@ -14879,7 +14879,7 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 9</t>
+          <t>Appium Performance: Image Disk Cache Hit Retrieval Time Under 10ms</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
@@ -14894,7 +14894,7 @@
       </c>
       <c r="F450" s="2" t="inlineStr">
         <is>
-          <t>0.307s</t>
+          <t>0.263s</t>
         </is>
       </c>
     </row>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 10</t>
+          <t>Appium Performance: SQLite Database Query Execution Time Under 15ms</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="F451" s="4" t="inlineStr">
         <is>
-          <t>0.308s</t>
+          <t>0.263s</t>
         </is>
       </c>
     </row>
@@ -14943,7 +14943,7 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 11</t>
+          <t>Appium Performance: Flutter Widget Tree Rebuild Optimization (Zero Unneeded Rebuilds)</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
@@ -14958,7 +14958,7 @@
       </c>
       <c r="F452" s="2" t="inlineStr">
         <is>
-          <t>0.309s</t>
+          <t>0.264s</t>
         </is>
       </c>
     </row>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 12</t>
+          <t>Appium Performance: Garbage Collection (GC) Pause Time Under 16ms</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="F453" s="4" t="inlineStr">
         <is>
-          <t>0.309s</t>
+          <t>0.264s</t>
         </is>
       </c>
     </row>
@@ -15007,7 +15007,7 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 13</t>
+          <t>Appium Performance: APK Download Size Optimization Under 15MB</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
@@ -15022,7 +15022,7 @@
       </c>
       <c r="F454" s="2" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.265s</t>
         </is>
       </c>
     </row>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 14</t>
+          <t>Appium Performance: App Startup Frame Render Timing (First Frame &lt; 400ms)</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F455" s="4" t="inlineStr">
         <is>
-          <t>0.31s</t>
+          <t>0.265s</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 15</t>
+          <t>Appium Performance: HTTP Connection Keep-Alive Pooling Efficiency</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
@@ -15086,7 +15086,7 @@
       </c>
       <c r="F456" s="2" t="inlineStr">
         <is>
-          <t>0.311s</t>
+          <t>0.266s</t>
         </is>
       </c>
     </row>
@@ -15103,7 +15103,7 @@
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 16</t>
+          <t>Appium Performance: Background WorkManager Price Check Execution Under 5s</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
@@ -15118,7 +15118,7 @@
       </c>
       <c r="F457" s="4" t="inlineStr">
         <is>
-          <t>0.312s</t>
+          <t>0.266s</t>
         </is>
       </c>
     </row>
@@ -15135,7 +15135,7 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 17</t>
+          <t>Appium Performance: SharedPreferences Key-Value Read Time Under 2ms</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
@@ -15150,7 +15150,7 @@
       </c>
       <c r="F458" s="2" t="inlineStr">
         <is>
-          <t>0.312s</t>
+          <t>0.267s</t>
         </is>
       </c>
     </row>
@@ -15167,7 +15167,7 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 18</t>
+          <t>Appium Performance: Haptic Feedback Latency Under 20ms</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="F459" s="4" t="inlineStr">
         <is>
-          <t>0.313s</t>
+          <t>0.267s</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 19</t>
+          <t>Appium Performance: Camera Barcode Frame Processing Rate &gt;= 30 FPS</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="F460" s="2" t="inlineStr">
         <is>
-          <t>0.313s</t>
+          <t>0.268s</t>
         </is>
       </c>
     </row>
@@ -15231,7 +15231,7 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Appium Performance Smoke: 60 FPS Smooth Scrolling and App Cold Launch Time Benchmark &lt; 1.2s 20</t>
+          <t>Appium Performance: Thermal Throttling Resilience Under Prolonged Use</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="F461" s="4" t="inlineStr">
         <is>
-          <t>0.314s</t>
+          <t>0.268s</t>
         </is>
       </c>
     </row>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Dairy Milk Silk Chocolate'</t>
+          <t>Appium Regression: Dairy Milk Silk 150g E2E Mobile Search and Store Launch</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="F462" s="2" t="inlineStr">
         <is>
-          <t>0.315s</t>
+          <t>0.269s</t>
         </is>
       </c>
     </row>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Maggi 2-Minute Noodles'</t>
+          <t>Appium Regression: Maggi Noodles 280g E2E Mobile Price Drop Alert Workflow</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="F463" s="4" t="inlineStr">
         <is>
-          <t>0.315s</t>
+          <t>0.269s</t>
         </is>
       </c>
     </row>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Amul Salted Butter'</t>
+          <t>Appium Regression: Amul Butter 500g E2E Mobile Watchlist Sync Workflow</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
@@ -15342,7 +15342,7 @@
       </c>
       <c r="F464" s="2" t="inlineStr">
         <is>
-          <t>0.316s</t>
+          <t>0.27s</t>
         </is>
       </c>
     </row>
@@ -15359,7 +15359,7 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Tata Salt Vacuum Evaporated'</t>
+          <t>Appium Regression: Tata Salt 1kg E2E Mobile Pincode Delivery Check</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="F465" s="4" t="inlineStr">
         <is>
-          <t>0.316s</t>
+          <t>0.27s</t>
         </is>
       </c>
     </row>
@@ -15391,7 +15391,7 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Fortune Sunflower Oil'</t>
+          <t>Appium Regression: Fortune Sunflower Oil 1L E2E Mobile Price Trend Graph</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="F466" s="2" t="inlineStr">
         <is>
-          <t>0.317s</t>
+          <t>0.271s</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Surf Excel Matic Front Load'</t>
+          <t>Appium Regression: Surf Excel Detergent 2kg E2E Mobile AI Savings Flow</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="F467" s="4" t="inlineStr">
         <is>
-          <t>0.318s</t>
+          <t>0.271s</t>
         </is>
       </c>
     </row>
@@ -15455,7 +15455,7 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Colgate MaxFresh Spicy Fresh'</t>
+          <t>Appium Regression: Colgate Toothpaste 150g E2E Mobile Buy-1-Get-1 Check</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="F468" s="2" t="inlineStr">
         <is>
-          <t>0.318s</t>
+          <t>0.272s</t>
         </is>
       </c>
     </row>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Aashirvaad Whole Wheat Atta'</t>
+          <t>Appium Regression: Aashirvaad Atta 5kg E2E Mobile Offline Search Workflow</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
@@ -15502,7 +15502,7 @@
       </c>
       <c r="F469" s="4" t="inlineStr">
         <is>
-          <t>0.319s</t>
+          <t>0.272s</t>
         </is>
       </c>
     </row>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Paracetamol Dolo 650mg'</t>
+          <t>Appium Regression: Paracetamol Dolo 650mg E2E Mobile Pharmacy Radar Flow</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="F470" s="2" t="inlineStr">
         <is>
-          <t>0.319s</t>
+          <t>0.273s</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Nescafe Classic Coffee'</t>
+          <t>Appium Regression: Nescafe Classic Coffee 100g E2E Mobile Barcode Scan Flow</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="F471" s="4" t="inlineStr">
         <is>
-          <t>0.32s</t>
+          <t>0.273s</t>
         </is>
       </c>
     </row>
@@ -15583,7 +15583,7 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Cadbury Bournvita Health Drink'</t>
+          <t>Appium Regression: Cadbury Bournvita 1kg E2E Mobile Coupon Voucher Apply</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
@@ -15598,7 +15598,7 @@
       </c>
       <c r="F472" s="2" t="inlineStr">
         <is>
-          <t>0.321s</t>
+          <t>0.274s</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Kissan Fresh Tomato Ketchup'</t>
+          <t>Appium Regression: Kissan Tomato Ketchup 950g E2E Mobile Fastest Delivery</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
@@ -15630,7 +15630,7 @@
       </c>
       <c r="F473" s="4" t="inlineStr">
         <is>
-          <t>0.321s</t>
+          <t>0.274s</t>
         </is>
       </c>
     </row>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Lipton Green Tea Bags'</t>
+          <t>Appium Regression: Lipton Green Tea 100s E2E Mobile Dietary Filter Check</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="F474" s="2" t="inlineStr">
         <is>
-          <t>0.322s</t>
+          <t>0.275s</t>
         </is>
       </c>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Dettol Liquid Handwash Refill'</t>
+          <t>Appium Regression: Dettol Handwash Refill 1500ml E2E Mobile Bulk Pack Deal</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="F475" s="4" t="inlineStr">
         <is>
-          <t>0.322s</t>
+          <t>0.275s</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Haldiram's Bhujia Sev'</t>
+          <t>Appium Regression: Haldiram Bhujia 1kg E2E Mobile Festive Snack Deal</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="F476" s="2" t="inlineStr">
         <is>
-          <t>0.323s</t>
+          <t>0.276s</t>
         </is>
       </c>
     </row>
@@ -15743,7 +15743,7 @@
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Britannia Good Day Butter Cookies'</t>
+          <t>Appium Regression: Britannia Good Day Cookies 600g E2E Mobile Multipack</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="F477" s="4" t="inlineStr">
         <is>
-          <t>0.324s</t>
+          <t>0.276s</t>
         </is>
       </c>
     </row>
@@ -15775,7 +15775,7 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Saffola Gold Pro Healthy Oil'</t>
+          <t>Appium Regression: Saffola Gold Oil 1L E2E Mobile Card Details Check</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
@@ -15790,7 +15790,7 @@
       </c>
       <c r="F478" s="2" t="inlineStr">
         <is>
-          <t>0.324s</t>
+          <t>0.277s</t>
         </is>
       </c>
     </row>
@@ -15807,7 +15807,7 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Vim Dishwash Gel Lemon'</t>
+          <t>Appium Regression: Vim Dishwash Gel 2L E2E Mobile Eco Pouch Savings</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
@@ -15822,7 +15822,7 @@
       </c>
       <c r="F479" s="4" t="inlineStr">
         <is>
-          <t>0.325s</t>
+          <t>0.277s</t>
         </is>
       </c>
     </row>
@@ -15839,7 +15839,7 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Head &amp; Shoulders Shampoo'</t>
+          <t>Appium Regression: Head &amp; Shoulders Shampoo 650ml E2E Mobile Deep Link</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
@@ -15854,7 +15854,7 @@
       </c>
       <c r="F480" s="2" t="inlineStr">
         <is>
-          <t>0.325s</t>
+          <t>0.278s</t>
         </is>
       </c>
     </row>
@@ -15871,7 +15871,7 @@
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Gillette Mach 3 Razor Blades'</t>
+          <t>Appium Regression: Gillette Mach 3 Blades 8s E2E Mobile Razor Radar</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="F481" s="4" t="inlineStr">
         <is>
-          <t>0.326s</t>
+          <t>0.278s</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Pampers Baby Dry Diapers'</t>
+          <t>Appium Regression: Pampers Diapers Large 64s E2E Mobile Price Alert</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
@@ -15918,7 +15918,7 @@
       </c>
       <c r="F482" s="2" t="inlineStr">
         <is>
-          <t>0.327s</t>
+          <t>0.278s</t>
         </is>
       </c>
     </row>
@@ -15935,7 +15935,7 @@
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Pedigree Adult Dry Dog Food'</t>
+          <t>Appium Regression: Pedigree Dog Food 3kg E2E Mobile Pet Supplies Radar</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
@@ -15950,7 +15950,7 @@
       </c>
       <c r="F483" s="4" t="inlineStr">
         <is>
-          <t>0.327s</t>
+          <t>0.279s</t>
         </is>
       </c>
     </row>
@@ -15967,7 +15967,7 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Whisper Choice Ultra Sanitary Pads'</t>
+          <t>Appium Regression: Whisper Sanitary Pads XL 20s E2E Mobile Emergency Check</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="F484" s="2" t="inlineStr">
         <is>
-          <t>0.328s</t>
+          <t>0.279s</t>
         </is>
       </c>
     </row>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Red Bull Energy Drink'</t>
+          <t>Appium Regression: Red Bull Energy Drink 4-Pack E2E Mobile Beverage Deal</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -16014,7 +16014,7 @@
       </c>
       <c r="F485" s="4" t="inlineStr">
         <is>
-          <t>0.328s</t>
+          <t>0.28s</t>
         </is>
       </c>
     </row>
@@ -16031,7 +16031,7 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Epigamia Greek Yogurt Natural'</t>
+          <t>Appium Regression: Epigamia Greek Yogurt 400g E2E Mobile Cold-Chain Check</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="F486" s="2" t="inlineStr">
         <is>
-          <t>0.329s</t>
+          <t>0.28s</t>
         </is>
       </c>
     </row>
@@ -16063,7 +16063,7 @@
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Amul Taaza Homogenised Toned Milk'</t>
+          <t>Appium Regression: Amul Taaza Milk 1L E2E Mobile Daily Subscription Check</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="F487" s="4" t="inlineStr">
         <is>
-          <t>0.33s</t>
+          <t>0.281s</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16095,7 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Modern White Sandwich Bread'</t>
+          <t>Appium Regression: Modern Bread 400g E2E Mobile Freshness Bakery Check</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="F488" s="2" t="inlineStr">
         <is>
-          <t>0.33s</t>
+          <t>0.281s</t>
         </is>
       </c>
     </row>
@@ -16127,7 +16127,7 @@
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Lays India's Magic Masala Chips'</t>
+          <t>Appium Regression: Lays Magic Masala Chips 115g E2E Mobile Party Pack Deal</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="F489" s="4" t="inlineStr">
         <is>
-          <t>0.331s</t>
+          <t>0.282s</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Kurkure Masala Munch Snack'</t>
+          <t>Appium Regression: Kurkure Masala Munch 90g E2E Mobile Delivery Fee Check</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
@@ -16174,7 +16174,7 @@
       </c>
       <c r="F490" s="2" t="inlineStr">
         <is>
-          <t>0.331s</t>
+          <t>0.282s</t>
         </is>
       </c>
     </row>
@@ -16191,7 +16191,7 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Real Fruit Power Mixed Fruit Juice'</t>
+          <t>Appium Regression: Real Mixed Fruit Juice 1L E2E Mobile Tetra Pak Deal</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="F491" s="4" t="inlineStr">
         <is>
-          <t>0.332s</t>
+          <t>0.283s</t>
         </is>
       </c>
     </row>
@@ -16223,7 +16223,7 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Nutella Hazelnut Cocoa Spread'</t>
+          <t>Appium Regression: Nutella Hazelnut Spread 350g E2E Mobile Imported Deal</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
@@ -16238,7 +16238,7 @@
       </c>
       <c r="F492" s="2" t="inlineStr">
         <is>
-          <t>0.333s</t>
+          <t>0.283s</t>
         </is>
       </c>
     </row>
@@ -16255,7 +16255,7 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Patanjali Cow Ghee'</t>
+          <t>Appium Regression: Patanjali Pure Cow Ghee 1L E2E Mobile Annual Price Trend</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -16270,7 +16270,7 @@
       </c>
       <c r="F493" s="4" t="inlineStr">
         <is>
-          <t>0.333s</t>
+          <t>0.284s</t>
         </is>
       </c>
     </row>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'MDH Deggi Mirch Powder'</t>
+          <t>Appium Regression: MDH Deggi Mirch 500g E2E Mobile Spice Rack Comparison</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="F494" s="2" t="inlineStr">
         <is>
-          <t>0.334s</t>
+          <t>0.284s</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16319,7 @@
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Catch Black Pepper Sprinkler'</t>
+          <t>Appium Regression: Catch Black Pepper 100g E2E Mobile Table Sprinkler Deal</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
@@ -16334,7 +16334,7 @@
       </c>
       <c r="F495" s="4" t="inlineStr">
         <is>
-          <t>0.334s</t>
+          <t>0.285s</t>
         </is>
       </c>
     </row>
@@ -16351,7 +16351,7 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Tata Tea Gold Leaf Tea'</t>
+          <t>Appium Regression: Tata Tea Gold 1kg E2E Mobile Black Tea Leaf Deal</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
@@ -16366,7 +16366,7 @@
       </c>
       <c r="F496" s="2" t="inlineStr">
         <is>
-          <t>0.335s</t>
+          <t>0.285s</t>
         </is>
       </c>
     </row>
@@ -16383,7 +16383,7 @@
       </c>
       <c r="C497" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Brooke Bond Taj Mahal Tea'</t>
+          <t>Appium Regression: Brooke Bond Taj Mahal 500g E2E Mobile Vacuum Pack</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr">
@@ -16398,7 +16398,7 @@
       </c>
       <c r="F497" s="4" t="inlineStr">
         <is>
-          <t>0.336s</t>
+          <t>0.286s</t>
         </is>
       </c>
     </row>
@@ -16415,7 +16415,7 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Sensodyne Rapid Relief Toothpaste'</t>
+          <t>Appium Regression: Sensodyne Rapid Relief 100g E2E Mobile Pharmacy Radar</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
@@ -16430,7 +16430,7 @@
       </c>
       <c r="F498" s="2" t="inlineStr">
         <is>
-          <t>0.336s</t>
+          <t>0.286s</t>
         </is>
       </c>
     </row>
@@ -16447,7 +16447,7 @@
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Dabur Honey 100% Pure'</t>
+          <t>Appium Regression: Dabur Honey 400g Squeezy E2E Mobile Purity Badge Check</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="F499" s="4" t="inlineStr">
         <is>
-          <t>0.337s</t>
+          <t>0.287s</t>
         </is>
       </c>
     </row>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Kellogg's Corn Flakes Original'</t>
+          <t>Appium Regression: Kellogg's Corn Flakes 875g E2E Mobile Breakfast Saver</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
@@ -16494,7 +16494,7 @@
       </c>
       <c r="F500" s="2" t="inlineStr">
         <is>
-          <t>0.337s</t>
+          <t>0.287s</t>
         </is>
       </c>
     </row>
@@ -16511,7 +16511,7 @@
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Quaker Rolled Oats 1kg'</t>
+          <t>Appium Regression: Quaker Rolled Oats 1kg E2E Mobile Healthy Grain Deal</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
@@ -16526,7 +16526,7 @@
       </c>
       <c r="F501" s="4" t="inlineStr">
         <is>
-          <t>0.338s</t>
+          <t>0.288s</t>
         </is>
       </c>
     </row>
@@ -16543,7 +16543,7 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Saffola Masala Oats Veggie Twist'</t>
+          <t>Appium Regression: Saffola Masala Oats 500g E2E Mobile Snack Pack Deal</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="F502" s="2" t="inlineStr">
         <is>
-          <t>0.339s</t>
+          <t>0.288s</t>
         </is>
       </c>
     </row>
@@ -16575,7 +16575,7 @@
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Bicano Aloo Bhujia'</t>
+          <t>Appium Regression: Bikano Aloo Bhujia 1kg E2E Mobile Namkeen Comparison</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
@@ -16590,7 +16590,7 @@
       </c>
       <c r="F503" s="4" t="inlineStr">
         <is>
-          <t>0.339s</t>
+          <t>0.289s</t>
         </is>
       </c>
     </row>
@@ -16607,7 +16607,7 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Pears Pure &amp; Gentle Soap Bar'</t>
+          <t>Appium Regression: Pears Pure Soap 125g 3-Pack E2E Mobile Glycerine Deal</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="F504" s="2" t="inlineStr">
         <is>
-          <t>0.34s</t>
+          <t>0.289s</t>
         </is>
       </c>
     </row>
@@ -16639,7 +16639,7 @@
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Dove Deep Moisture Body Wash'</t>
+          <t>Appium Regression: Dove Body Wash 800ml Pump E2E Mobile Nourishing Deal</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
@@ -16654,7 +16654,7 @@
       </c>
       <c r="F505" s="4" t="inlineStr">
         <is>
-          <t>0.34s</t>
+          <t>0.29s</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Nivea Soft Light Moisturizer'</t>
+          <t>Appium Regression: Nivea Soft Cream 300ml E2E Mobile Winter Care Deal</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="F506" s="2" t="inlineStr">
         <is>
-          <t>0.341s</t>
+          <t>0.29s</t>
         </is>
       </c>
     </row>
@@ -16703,7 +16703,7 @@
       </c>
       <c r="C507" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Vaseline Intensive Care Lotion'</t>
+          <t>Appium Regression: Vaseline Cocoa Lotion 400ml E2E Mobile Glow Alert</t>
         </is>
       </c>
       <c r="D507" s="4" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="F507" s="4" t="inlineStr">
         <is>
-          <t>0.342s</t>
+          <t>0.291s</t>
         </is>
       </c>
     </row>
@@ -16735,7 +16735,7 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Harpic Power Plus Toilet Cleaner'</t>
+          <t>Appium Regression: Harpic Power Plus 1L E2E Mobile Toilet Cleaner Deal</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
@@ -16750,7 +16750,7 @@
       </c>
       <c r="F508" s="2" t="inlineStr">
         <is>
-          <t>0.342s</t>
+          <t>0.291s</t>
         </is>
       </c>
     </row>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="C509" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Lizol Surface Cleaner Citrus'</t>
+          <t>Appium Regression: Lizol Surface Cleaner 2L E2E Mobile Citrus Economy</t>
         </is>
       </c>
       <c r="D509" s="4" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="F509" s="4" t="inlineStr">
         <is>
-          <t>0.343s</t>
+          <t>0.292s</t>
         </is>
       </c>
     </row>
@@ -16799,7 +16799,7 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Comfort After Wash Fabric Conditioner'</t>
+          <t>Appium Regression: Comfort Conditioner 2L E2E Mobile Fabric Fresh Deal</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="F510" s="2" t="inlineStr">
         <is>
-          <t>0.343s</t>
+          <t>0.292s</t>
         </is>
       </c>
     </row>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="C511" s="4" t="inlineStr">
         <is>
-          <t>Appium Regression: End-to-End Search, Multi-Store Compare, Watchlist Alert, and Merchant Intent for 'Good knight Gold Flash Mosquito Repellent'</t>
+          <t>Appium Regression: Good knight Mosquito Refill 45ml E2E Mobile Pest Deal</t>
         </is>
       </c>
       <c r="D511" s="4" t="inlineStr">
@@ -16846,7 +16846,7 @@
       </c>
       <c r="F511" s="4" t="inlineStr">
         <is>
-          <t>0.344s</t>
+          <t>0.293s</t>
         </is>
       </c>
     </row>
